--- a/Suivi_Comportemental_Challenger.xlsx
+++ b/Suivi_Comportemental_Challenger.xlsx
@@ -1,17 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D31364-7D28-4925-ACCB-C2CD0338F356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="Donnees Brutes" sheetId="1" r:id="rId1"/>
-    <sheet name="Par Champion" sheetId="2" r:id="rId2"/>
-    <sheet name="Solo vs Duo" sheetId="3" r:id="rId3"/>
-    <sheet name="Tendances Comportementales" sheetId="4" r:id="rId4"/>
+    <sheet sheetId="1" name="Donnees Brutes" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Par Champion" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Solo vs Duo" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Tendances Comportementales" state="visible" r:id="rId7"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
@@ -1895,7 +1891,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
@@ -1903,74 +1899,63 @@
   </numFmts>
   <fonts count="12" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <sz val="10"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF991B1B"/>
-      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFA855F7"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF166534"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFB45309"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFA855F7"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF166534"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFB45309"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <i/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FF4F46E5"/>
       <sz val="10"/>
-      <color rgb="FF4F46E5"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="19">
@@ -2188,6 +2173,9 @@
     <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2215,30 +2203,27 @@
     <xf numFmtId="165" fontId="2" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="2" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="11" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="11" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2577,9 +2562,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AT204"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="7" customWidth="1"/>
@@ -2594,7 +2579,6 @@
     <col min="14" max="17" width="8" customWidth="1"/>
     <col min="18" max="18" width="7" customWidth="1"/>
     <col min="19" max="19" width="8" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" bestFit="1" customWidth="1"/>
     <col min="21" max="23" width="8" customWidth="1"/>
     <col min="25" max="26" width="10" customWidth="1"/>
     <col min="27" max="29" width="7" customWidth="1"/>
@@ -2610,7 +2594,7 @@
     <col min="46" max="46" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2750,7 +2734,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>46</v>
       </c>
@@ -2794,7 +2778,7 @@
         <v>15.7</v>
       </c>
       <c r="O2" s="14">
-        <v>68.900000000000006</v>
+        <v>68.9</v>
       </c>
       <c r="P2" s="14">
         <v>42.3</v>
@@ -2890,7 +2874,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A3" s="17" t="s">
         <v>46</v>
       </c>
@@ -3030,7 +3014,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="4" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>46</v>
       </c>
@@ -3080,7 +3064,7 @@
         <v>31.3</v>
       </c>
       <c r="Q4" s="14">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="R4" s="15">
         <v>506</v>
@@ -3170,7 +3154,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A5" s="17" t="s">
         <v>64</v>
       </c>
@@ -3310,7 +3294,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>64</v>
       </c>
@@ -3450,7 +3434,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
         <v>64</v>
       </c>
@@ -3590,7 +3574,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="8" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>64</v>
       </c>
@@ -3619,7 +3603,7 @@
         <v>52</v>
       </c>
       <c r="J8" s="28">
-        <v>0.14000000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="K8" s="10">
         <v>1</v>
@@ -3730,7 +3714,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="9" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>64</v>
       </c>
@@ -3780,7 +3764,7 @@
         <v>36.4</v>
       </c>
       <c r="Q9" s="21">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="R9" s="23">
         <v>501</v>
@@ -3870,7 +3854,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>64</v>
       </c>
@@ -3911,16 +3895,16 @@
         <v>13</v>
       </c>
       <c r="N10" s="14">
-        <v>16.399999999999999</v>
+        <v>16.4</v>
       </c>
       <c r="O10" s="14">
-        <v>65.400000000000006</v>
+        <v>65.4</v>
       </c>
       <c r="P10" s="14">
         <v>39.9</v>
       </c>
       <c r="Q10" s="14">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="R10" s="15">
         <v>653</v>
@@ -4010,7 +3994,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="11" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A11" s="17" t="s">
         <v>64</v>
       </c>
@@ -4057,7 +4041,7 @@
         <v>66.7</v>
       </c>
       <c r="P11" s="21">
-        <v>37.700000000000003</v>
+        <v>37.7</v>
       </c>
       <c r="Q11" s="32">
         <v>9.1</v>
@@ -4150,7 +4134,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>64</v>
       </c>
@@ -4290,7 +4274,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A13" s="17" t="s">
         <v>88</v>
       </c>
@@ -4331,13 +4315,13 @@
         <v>3</v>
       </c>
       <c r="N13" s="21">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="O13" s="21">
         <v>62.5</v>
       </c>
       <c r="P13" s="21">
-        <v>40.200000000000003</v>
+        <v>40.2</v>
       </c>
       <c r="Q13" s="32">
         <v>10.7</v>
@@ -4430,7 +4414,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
         <v>88</v>
       </c>
@@ -4471,7 +4455,7 @@
         <v>11</v>
       </c>
       <c r="N14" s="29">
-        <v>20.399999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="O14" s="14">
         <v>57.6</v>
@@ -4570,7 +4554,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="15" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>88</v>
       </c>
@@ -4710,7 +4694,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="16" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
         <v>88</v>
       </c>
@@ -4850,7 +4834,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A17" s="17" t="s">
         <v>88</v>
       </c>
@@ -4990,7 +4974,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="18" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>88</v>
       </c>
@@ -5031,10 +5015,10 @@
         <v>3</v>
       </c>
       <c r="N18" s="14">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="O18" s="14">
-        <v>39.299999999999997</v>
+        <v>39.3</v>
       </c>
       <c r="P18" s="14">
         <v>31.5</v>
@@ -5130,7 +5114,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="19" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A19" s="17" t="s">
         <v>88</v>
       </c>
@@ -5177,7 +5161,7 @@
         <v>55.2</v>
       </c>
       <c r="P19" s="21">
-        <v>33.799999999999997</v>
+        <v>33.8</v>
       </c>
       <c r="Q19" s="32">
         <v>9.1</v>
@@ -5270,7 +5254,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>88</v>
       </c>
@@ -5317,7 +5301,7 @@
         <v>80</v>
       </c>
       <c r="P20" s="14">
-        <v>40.700000000000003</v>
+        <v>40.7</v>
       </c>
       <c r="Q20" s="32">
         <v>11.2</v>
@@ -5410,7 +5394,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>88</v>
       </c>
@@ -5451,7 +5435,7 @@
         <v>2</v>
       </c>
       <c r="N21" s="21">
-        <v>8.6999999999999993</v>
+        <v>8.7</v>
       </c>
       <c r="O21" s="21">
         <v>51.4</v>
@@ -5550,7 +5534,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="22" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>106</v>
       </c>
@@ -5690,7 +5674,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A23" s="17" t="s">
         <v>106</v>
       </c>
@@ -5830,7 +5814,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>106</v>
       </c>
@@ -5970,7 +5954,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A25" s="17" t="s">
         <v>106</v>
       </c>
@@ -6014,10 +5998,10 @@
         <v>7.8</v>
       </c>
       <c r="O25" s="21">
-        <v>75.599999999999994</v>
+        <v>75.6</v>
       </c>
       <c r="P25" s="21">
-        <v>39.200000000000003</v>
+        <v>39.2</v>
       </c>
       <c r="Q25" s="21">
         <v>7</v>
@@ -6110,7 +6094,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>106</v>
       </c>
@@ -6157,7 +6141,7 @@
         <v>70.3</v>
       </c>
       <c r="P26" s="14">
-        <v>38.299999999999997</v>
+        <v>38.3</v>
       </c>
       <c r="Q26" s="32">
         <v>11.1</v>
@@ -6250,7 +6234,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="27" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>106</v>
       </c>
@@ -6291,7 +6275,7 @@
         <v>8</v>
       </c>
       <c r="N27" s="21">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="O27" s="21">
         <v>75</v>
@@ -6300,7 +6284,7 @@
         <v>39.5</v>
       </c>
       <c r="Q27" s="21">
-        <v>8.6999999999999993</v>
+        <v>8.7</v>
       </c>
       <c r="R27" s="23">
         <v>585</v>
@@ -6390,7 +6374,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="28" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>106</v>
       </c>
@@ -6437,7 +6421,7 @@
         <v>66.7</v>
       </c>
       <c r="P28" s="14">
-        <v>37.799999999999997</v>
+        <v>37.8</v>
       </c>
       <c r="Q28" s="22">
         <v>5.3</v>
@@ -6530,7 +6514,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A29" s="17" t="s">
         <v>106</v>
       </c>
@@ -6571,7 +6555,7 @@
         <v>5</v>
       </c>
       <c r="N29" s="21">
-        <v>9.6999999999999993</v>
+        <v>9.7</v>
       </c>
       <c r="O29" s="21">
         <v>47.1</v>
@@ -6670,7 +6654,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="30" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>106</v>
       </c>
@@ -6810,7 +6794,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="31" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A31" s="17" t="s">
         <v>106</v>
       </c>
@@ -6950,7 +6934,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="32" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>106</v>
       </c>
@@ -7090,7 +7074,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>106</v>
       </c>
@@ -7137,7 +7121,7 @@
         <v>76</v>
       </c>
       <c r="P33" s="21">
-        <v>38.299999999999997</v>
+        <v>38.3</v>
       </c>
       <c r="Q33" s="22">
         <v>6.8</v>
@@ -7230,7 +7214,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="34" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>106</v>
       </c>
@@ -7370,7 +7354,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>137</v>
       </c>
@@ -7510,7 +7494,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="36" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>137</v>
       </c>
@@ -7650,7 +7634,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A37" s="17" t="s">
         <v>137</v>
       </c>
@@ -7694,7 +7678,7 @@
         <v>10.1</v>
       </c>
       <c r="O37" s="21">
-        <v>36.799999999999997</v>
+        <v>36.8</v>
       </c>
       <c r="P37" s="21">
         <v>17.8</v>
@@ -7790,7 +7774,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="38" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>137</v>
       </c>
@@ -7840,7 +7824,7 @@
         <v>29.1</v>
       </c>
       <c r="Q38" s="22">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="R38" s="15">
         <v>498</v>
@@ -7930,7 +7914,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="39" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>137</v>
       </c>
@@ -8070,7 +8054,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
         <v>137</v>
       </c>
@@ -8210,7 +8194,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A41" s="17" t="s">
         <v>137</v>
       </c>
@@ -8350,7 +8334,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
         <v>137</v>
       </c>
@@ -8394,7 +8378,7 @@
         <v>14</v>
       </c>
       <c r="O42" s="14">
-        <v>71.099999999999994</v>
+        <v>71.1</v>
       </c>
       <c r="P42" s="14">
         <v>21</v>
@@ -8490,7 +8474,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A43" s="17" t="s">
         <v>156</v>
       </c>
@@ -8630,7 +8614,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>156</v>
       </c>
@@ -8770,7 +8754,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>156</v>
       </c>
@@ -8910,7 +8894,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>156</v>
       </c>
@@ -9050,7 +9034,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="47" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A47" s="17" t="s">
         <v>156</v>
       </c>
@@ -9100,7 +9084,7 @@
         <v>20.2</v>
       </c>
       <c r="Q47" s="22">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="R47" s="23">
         <v>340</v>
@@ -9190,7 +9174,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="48" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>156</v>
       </c>
@@ -9330,7 +9314,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="49" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
         <v>156</v>
       </c>
@@ -9377,7 +9361,7 @@
         <v>64.3</v>
       </c>
       <c r="P49" s="21">
-        <v>20.100000000000001</v>
+        <v>20.1</v>
       </c>
       <c r="Q49" s="22">
         <v>5.4</v>
@@ -9470,7 +9454,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>156</v>
       </c>
@@ -9610,7 +9594,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
         <v>177</v>
       </c>
@@ -9750,7 +9734,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>180</v>
       </c>
@@ -9797,7 +9781,7 @@
         <v>75</v>
       </c>
       <c r="P52" s="14">
-        <v>19.899999999999999</v>
+        <v>19.9</v>
       </c>
       <c r="Q52" s="22">
         <v>4.5</v>
@@ -9890,7 +9874,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A53" s="17" t="s">
         <v>180</v>
       </c>
@@ -9940,7 +9924,7 @@
         <v>42.4</v>
       </c>
       <c r="Q53" s="21">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="R53" s="23">
         <v>663</v>
@@ -10030,7 +10014,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="54" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>180</v>
       </c>
@@ -10080,7 +10064,7 @@
         <v>25.2</v>
       </c>
       <c r="Q54" s="32">
-        <v>9.6999999999999993</v>
+        <v>9.7</v>
       </c>
       <c r="R54" s="15">
         <v>572</v>
@@ -10170,7 +10154,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A55" s="17" t="s">
         <v>180</v>
       </c>
@@ -10310,7 +10294,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="56" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
         <v>180</v>
       </c>
@@ -10450,7 +10434,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="57" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
         <v>180</v>
       </c>
@@ -10590,7 +10574,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="58" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
         <v>194</v>
       </c>
@@ -10730,7 +10714,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="59" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A59" s="17" t="s">
         <v>194</v>
       </c>
@@ -10870,7 +10854,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A60" s="9" t="s">
         <v>194</v>
       </c>
@@ -10920,7 +10904,7 @@
         <v>25.7</v>
       </c>
       <c r="Q60" s="14">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="R60" s="15">
         <v>673</v>
@@ -11010,7 +10994,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="61" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A61" s="17" t="s">
         <v>194</v>
       </c>
@@ -11054,7 +11038,7 @@
         <v>13.9</v>
       </c>
       <c r="O61" s="21">
-        <v>69.599999999999994</v>
+        <v>69.6</v>
       </c>
       <c r="P61" s="21">
         <v>35.4</v>
@@ -11150,7 +11134,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="62" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
         <v>194</v>
       </c>
@@ -11290,7 +11274,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="63" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A63" s="17" t="s">
         <v>194</v>
       </c>
@@ -11430,7 +11414,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A64" s="9" t="s">
         <v>205</v>
       </c>
@@ -11480,7 +11464,7 @@
         <v>27.9</v>
       </c>
       <c r="Q64" s="14">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="R64" s="15">
         <v>493</v>
@@ -11570,7 +11554,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="65" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A65" s="17" t="s">
         <v>205</v>
       </c>
@@ -11617,10 +11601,10 @@
         <v>55.6</v>
       </c>
       <c r="P65" s="21">
-        <v>39.200000000000003</v>
+        <v>39.2</v>
       </c>
       <c r="Q65" s="32">
-        <v>10.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="R65" s="23">
         <v>673</v>
@@ -11710,7 +11694,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="66" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
         <v>205</v>
       </c>
@@ -11760,7 +11744,7 @@
         <v>31.2</v>
       </c>
       <c r="Q66" s="14">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="R66" s="15">
         <v>498</v>
@@ -11850,7 +11834,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="67" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A67" s="17" t="s">
         <v>205</v>
       </c>
@@ -11990,7 +11974,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="68" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A68" s="9" t="s">
         <v>205</v>
       </c>
@@ -12130,7 +12114,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="69" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A69" s="17" t="s">
         <v>205</v>
       </c>
@@ -12171,7 +12155,7 @@
         <v>1</v>
       </c>
       <c r="N69" s="21">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="O69" s="21">
         <v>58.8</v>
@@ -12270,7 +12254,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
         <v>219</v>
       </c>
@@ -12299,7 +12283,7 @@
         <v>52</v>
       </c>
       <c r="J70" s="12">
-        <v>2.4300000000000002</v>
+        <v>2.43</v>
       </c>
       <c r="K70" s="10">
         <v>21</v>
@@ -12410,7 +12394,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="71" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A71" s="17" t="s">
         <v>219</v>
       </c>
@@ -12550,7 +12534,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="72" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
         <v>219</v>
       </c>
@@ -12597,7 +12581,7 @@
         <v>60.9</v>
       </c>
       <c r="P72" s="14">
-        <v>17.600000000000001</v>
+        <v>17.6</v>
       </c>
       <c r="Q72" s="22">
         <v>6.8</v>
@@ -12690,7 +12674,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A73" s="17" t="s">
         <v>219</v>
       </c>
@@ -12734,7 +12718,7 @@
         <v>14.7</v>
       </c>
       <c r="O73" s="21">
-        <v>67.599999999999994</v>
+        <v>67.6</v>
       </c>
       <c r="P73" s="21">
         <v>24</v>
@@ -12830,7 +12814,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="74" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
         <v>219</v>
       </c>
@@ -12880,7 +12864,7 @@
         <v>18.5</v>
       </c>
       <c r="Q74" s="14">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="R74" s="15">
         <v>532</v>
@@ -12970,7 +12954,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="75" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A75" s="17" t="s">
         <v>219</v>
       </c>
@@ -13110,7 +13094,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="76" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A76" s="9" t="s">
         <v>219</v>
       </c>
@@ -13160,7 +13144,7 @@
         <v>28.9</v>
       </c>
       <c r="Q76" s="14">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="R76" s="15">
         <v>382</v>
@@ -13250,7 +13234,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="77" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A77" s="17" t="s">
         <v>219</v>
       </c>
@@ -13390,7 +13374,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="78" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
         <v>219</v>
       </c>
@@ -13434,13 +13418,13 @@
         <v>6.9</v>
       </c>
       <c r="O78" s="14">
-        <v>64.099999999999994</v>
+        <v>64.1</v>
       </c>
       <c r="P78" s="14">
         <v>22.8</v>
       </c>
       <c r="Q78" s="14">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="R78" s="15">
         <v>552</v>
@@ -13530,7 +13514,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="79" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A79" s="17" t="s">
         <v>219</v>
       </c>
@@ -13571,10 +13555,10 @@
         <v>19</v>
       </c>
       <c r="N79" s="21">
-        <v>9.3000000000000007</v>
+        <v>9.3</v>
       </c>
       <c r="O79" s="21">
-        <v>67.400000000000006</v>
+        <v>67.4</v>
       </c>
       <c r="P79" s="21">
         <v>23.4</v>
@@ -13670,7 +13654,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="80" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
         <v>219</v>
       </c>
@@ -13810,7 +13794,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="81" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A81" s="17" t="s">
         <v>219</v>
       </c>
@@ -13854,7 +13838,7 @@
         <v>3.2</v>
       </c>
       <c r="O81" s="21">
-        <v>17.899999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="P81" s="21">
         <v>13.7</v>
@@ -13950,7 +13934,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="82" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A82" s="9" t="s">
         <v>242</v>
       </c>
@@ -13991,16 +13975,16 @@
         <v>6</v>
       </c>
       <c r="N82" s="14">
-        <v>9.3000000000000007</v>
+        <v>9.3</v>
       </c>
       <c r="O82" s="14">
         <v>56.5</v>
       </c>
       <c r="P82" s="14">
-        <v>32.700000000000003</v>
+        <v>32.7</v>
       </c>
       <c r="Q82" s="14">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="R82" s="15">
         <v>618</v>
@@ -14090,7 +14074,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="83" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A83" s="17" t="s">
         <v>242</v>
       </c>
@@ -14230,7 +14214,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="84" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
         <v>242</v>
       </c>
@@ -14274,7 +14258,7 @@
         <v>12.2</v>
       </c>
       <c r="O84" s="14">
-        <v>69.599999999999994</v>
+        <v>69.6</v>
       </c>
       <c r="P84" s="14">
         <v>33.9</v>
@@ -14370,7 +14354,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="85" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A85" s="17" t="s">
         <v>242</v>
       </c>
@@ -14411,7 +14395,7 @@
         <v>7</v>
       </c>
       <c r="N85" s="21">
-        <v>10.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="O85" s="21">
         <v>54.5</v>
@@ -14510,7 +14494,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="86" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A86" s="9" t="s">
         <v>242</v>
       </c>
@@ -14650,7 +14634,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="87" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A87" s="17" t="s">
         <v>242</v>
       </c>
@@ -14697,10 +14681,10 @@
         <v>64.7</v>
       </c>
       <c r="P87" s="21">
-        <v>35.200000000000003</v>
+        <v>35.2</v>
       </c>
       <c r="Q87" s="21">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="R87" s="23">
         <v>543</v>
@@ -14790,7 +14774,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="88" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
         <v>242</v>
       </c>
@@ -14930,7 +14914,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="89" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A89" s="17" t="s">
         <v>256</v>
       </c>
@@ -14959,7 +14943,7 @@
         <v>52</v>
       </c>
       <c r="J89" s="31">
-        <v>2.5499999999999998</v>
+        <v>2.55</v>
       </c>
       <c r="K89" s="18">
         <v>22</v>
@@ -15070,7 +15054,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="90" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A90" s="9" t="s">
         <v>256</v>
       </c>
@@ -15210,7 +15194,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="91" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A91" s="17" t="s">
         <v>256</v>
       </c>
@@ -15257,7 +15241,7 @@
         <v>58.1</v>
       </c>
       <c r="P91" s="21">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="Q91" s="21">
         <v>7.9</v>
@@ -15350,7 +15334,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="92" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
         <v>256</v>
       </c>
@@ -15490,7 +15474,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="93" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A93" s="17" t="s">
         <v>256</v>
       </c>
@@ -15537,7 +15521,7 @@
         <v>57.7</v>
       </c>
       <c r="P93" s="21">
-        <v>19.399999999999999</v>
+        <v>19.4</v>
       </c>
       <c r="Q93" s="21">
         <v>8</v>
@@ -15630,7 +15614,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="94" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A94" s="9" t="s">
         <v>256</v>
       </c>
@@ -15680,7 +15664,7 @@
         <v>23.9</v>
       </c>
       <c r="Q94" s="14">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="R94" s="15">
         <v>569</v>
@@ -15770,7 +15754,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="95" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A95" s="17" t="s">
         <v>256</v>
       </c>
@@ -15910,7 +15894,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="96" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A96" s="9" t="s">
         <v>256</v>
       </c>
@@ -16050,7 +16034,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="97" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A97" s="17" t="s">
         <v>256</v>
       </c>
@@ -16190,7 +16174,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="98" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A98" s="9" t="s">
         <v>274</v>
       </c>
@@ -16219,7 +16203,7 @@
         <v>52</v>
       </c>
       <c r="J98" s="28">
-        <v>1.1100000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="K98" s="10">
         <v>8</v>
@@ -16237,7 +16221,7 @@
         <v>52.6</v>
       </c>
       <c r="P98" s="14">
-        <v>35.799999999999997</v>
+        <v>35.8</v>
       </c>
       <c r="Q98" s="14">
         <v>7.5</v>
@@ -16330,7 +16314,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="99" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A99" s="17" t="s">
         <v>274</v>
       </c>
@@ -16470,7 +16454,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="100" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
         <v>274</v>
       </c>
@@ -16520,7 +16504,7 @@
         <v>53.7</v>
       </c>
       <c r="Q100" s="14">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="R100" s="15">
         <v>756</v>
@@ -16610,7 +16594,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="101" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A101" s="17" t="s">
         <v>274</v>
       </c>
@@ -16750,7 +16734,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="102" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
         <v>274</v>
       </c>
@@ -16890,7 +16874,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="103" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A103" s="17" t="s">
         <v>274</v>
       </c>
@@ -17030,7 +17014,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="104" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
         <v>274</v>
       </c>
@@ -17170,7 +17154,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="105" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A105" s="17" t="s">
         <v>287</v>
       </c>
@@ -17199,7 +17183,7 @@
         <v>52</v>
       </c>
       <c r="J105" s="31">
-        <v>2.5499999999999998</v>
+        <v>2.55</v>
       </c>
       <c r="K105" s="18">
         <v>16</v>
@@ -17310,7 +17294,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="106" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
         <v>287</v>
       </c>
@@ -17354,7 +17338,7 @@
         <v>12.6</v>
       </c>
       <c r="O106" s="14">
-        <v>35.700000000000003</v>
+        <v>35.7</v>
       </c>
       <c r="P106" s="14">
         <v>20.6</v>
@@ -17450,7 +17434,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="107" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A107" s="17" t="s">
         <v>287</v>
       </c>
@@ -17491,7 +17475,7 @@
         <v>3</v>
       </c>
       <c r="N107" s="21">
-        <v>18.100000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="O107" s="21">
         <v>44.4</v>
@@ -17590,7 +17574,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="108" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
         <v>287</v>
       </c>
@@ -17730,7 +17714,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="109" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A109" s="17" t="s">
         <v>287</v>
       </c>
@@ -17870,7 +17854,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="110" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A110" s="9" t="s">
         <v>287</v>
       </c>
@@ -18010,7 +17994,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="111" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A111" s="17" t="s">
         <v>287</v>
       </c>
@@ -18150,7 +18134,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="112" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
         <v>287</v>
       </c>
@@ -18290,7 +18274,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="113" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A113" s="17" t="s">
         <v>301</v>
       </c>
@@ -18331,7 +18315,7 @@
         <v>5</v>
       </c>
       <c r="N113" s="21">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="O113" s="21">
         <v>28.1</v>
@@ -18340,7 +18324,7 @@
         <v>21.9</v>
       </c>
       <c r="Q113" s="21">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="R113" s="23">
         <v>474</v>
@@ -18430,7 +18414,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="114" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A114" s="9" t="s">
         <v>301</v>
       </c>
@@ -18570,7 +18554,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="115" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A115" s="17" t="s">
         <v>301</v>
       </c>
@@ -18710,7 +18694,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="116" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
         <v>301</v>
       </c>
@@ -18850,7 +18834,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="117" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A117" s="17" t="s">
         <v>301</v>
       </c>
@@ -18891,7 +18875,7 @@
         <v>5</v>
       </c>
       <c r="N117" s="21">
-        <v>18.100000000000001</v>
+        <v>18.1</v>
       </c>
       <c r="O117" s="21">
         <v>77.8</v>
@@ -18990,7 +18974,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="118" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A118" s="9" t="s">
         <v>311</v>
       </c>
@@ -19130,7 +19114,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="119" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A119" s="17" t="s">
         <v>311</v>
       </c>
@@ -19270,7 +19254,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="120" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
         <v>311</v>
       </c>
@@ -19320,7 +19304,7 @@
         <v>5.9</v>
       </c>
       <c r="Q120" s="22">
-        <v>4.4000000000000004</v>
+        <v>4.4</v>
       </c>
       <c r="R120" s="15">
         <v>360</v>
@@ -19410,7 +19394,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="121" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A121" s="17" t="s">
         <v>311</v>
       </c>
@@ -19550,7 +19534,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="122" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A122" s="9" t="s">
         <v>311</v>
       </c>
@@ -19690,7 +19674,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="123" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A123" s="17" t="s">
         <v>311</v>
       </c>
@@ -19731,10 +19715,10 @@
         <v>4</v>
       </c>
       <c r="N123" s="21">
-        <v>8.6999999999999993</v>
+        <v>8.7</v>
       </c>
       <c r="O123" s="21">
-        <v>70.599999999999994</v>
+        <v>70.6</v>
       </c>
       <c r="P123" s="21">
         <v>47</v>
@@ -19830,7 +19814,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="124" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A124" s="9" t="s">
         <v>323</v>
       </c>
@@ -19970,7 +19954,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="125" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A125" s="17" t="s">
         <v>323</v>
       </c>
@@ -20110,7 +20094,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="126" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A126" s="9" t="s">
         <v>323</v>
       </c>
@@ -20250,7 +20234,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="127" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A127" s="17" t="s">
         <v>323</v>
       </c>
@@ -20390,7 +20374,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="128" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A128" s="9" t="s">
         <v>323</v>
       </c>
@@ -20437,7 +20421,7 @@
         <v>53.6</v>
       </c>
       <c r="P128" s="14">
-        <v>32.799999999999997</v>
+        <v>32.8</v>
       </c>
       <c r="Q128" s="32">
         <v>10.8</v>
@@ -20530,7 +20514,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="129" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A129" s="17" t="s">
         <v>323</v>
       </c>
@@ -20571,13 +20555,13 @@
         <v>8</v>
       </c>
       <c r="N129" s="21">
-        <v>16.600000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="O129" s="21">
         <v>56.6</v>
       </c>
       <c r="P129" s="21">
-        <v>35.799999999999997</v>
+        <v>35.8</v>
       </c>
       <c r="Q129" s="22">
         <v>6.4</v>
@@ -20670,7 +20654,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="130" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
         <v>323</v>
       </c>
@@ -20810,7 +20794,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="131" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A131" s="17" t="s">
         <v>323</v>
       </c>
@@ -20854,7 +20838,7 @@
         <v>11.8</v>
       </c>
       <c r="O131" s="21">
-        <v>76.099999999999994</v>
+        <v>76.1</v>
       </c>
       <c r="P131" s="21">
         <v>50.4</v>
@@ -20950,7 +20934,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="132" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A132" s="9" t="s">
         <v>323</v>
       </c>
@@ -21090,7 +21074,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="133" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A133" s="17" t="s">
         <v>343</v>
       </c>
@@ -21230,7 +21214,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="134" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A134" s="9" t="s">
         <v>343</v>
       </c>
@@ -21370,7 +21354,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="135" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A135" s="17" t="s">
         <v>343</v>
       </c>
@@ -21510,7 +21494,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="136" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A136" s="9" t="s">
         <v>343</v>
       </c>
@@ -21650,7 +21634,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="137" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A137" s="17" t="s">
         <v>343</v>
       </c>
@@ -21790,7 +21774,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="138" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A138" s="9" t="s">
         <v>343</v>
       </c>
@@ -21930,7 +21914,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="139" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A139" s="17" t="s">
         <v>343</v>
       </c>
@@ -21959,7 +21943,7 @@
         <v>52</v>
       </c>
       <c r="J139" s="28">
-        <v>1.1100000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="K139" s="18">
         <v>3</v>
@@ -22070,7 +22054,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="140" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A140" s="9" t="s">
         <v>343</v>
       </c>
@@ -22117,7 +22101,7 @@
         <v>54.5</v>
       </c>
       <c r="P140" s="14">
-        <v>18.600000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="Q140" s="22">
         <v>6</v>
@@ -22210,7 +22194,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="141" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A141" s="17" t="s">
         <v>343</v>
       </c>
@@ -22254,10 +22238,10 @@
         <v>4.7</v>
       </c>
       <c r="O141" s="21">
-        <v>72.400000000000006</v>
+        <v>72.4</v>
       </c>
       <c r="P141" s="21">
-        <v>33.799999999999997</v>
+        <v>33.8</v>
       </c>
       <c r="Q141" s="32">
         <v>9.1</v>
@@ -22350,7 +22334,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="142" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A142" s="9" t="s">
         <v>343</v>
       </c>
@@ -22391,7 +22375,7 @@
         <v>8</v>
       </c>
       <c r="N142" s="14">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="O142" s="14">
         <v>52.5</v>
@@ -22400,7 +22384,7 @@
         <v>30.5</v>
       </c>
       <c r="Q142" s="14">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="R142" s="15">
         <v>615</v>
@@ -22490,7 +22474,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="143" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A143" s="17" t="s">
         <v>343</v>
       </c>
@@ -22630,7 +22614,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="144" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A144" s="9" t="s">
         <v>365</v>
       </c>
@@ -22770,7 +22754,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="145" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A145" s="17" t="s">
         <v>365</v>
       </c>
@@ -22910,7 +22894,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="146" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A146" s="9" t="s">
         <v>365</v>
       </c>
@@ -23050,7 +23034,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="147" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A147" s="17" t="s">
         <v>365</v>
       </c>
@@ -23190,7 +23174,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="148" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A148" s="9" t="s">
         <v>365</v>
       </c>
@@ -23330,7 +23314,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="149" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A149" s="17" t="s">
         <v>374</v>
       </c>
@@ -23470,7 +23454,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="150" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
         <v>374</v>
       </c>
@@ -23610,7 +23594,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A151" s="17" t="s">
         <v>374</v>
       </c>
@@ -23750,7 +23734,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="152" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A152" s="9" t="s">
         <v>374</v>
       </c>
@@ -23890,7 +23874,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="153" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A153" s="17" t="s">
         <v>374</v>
       </c>
@@ -24030,7 +24014,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="154" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A154" s="9" t="s">
         <v>374</v>
       </c>
@@ -24170,7 +24154,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="155" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A155" s="17" t="s">
         <v>383</v>
       </c>
@@ -24220,7 +24204,7 @@
         <v>27.6</v>
       </c>
       <c r="Q155" s="21">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="R155" s="23">
         <v>506</v>
@@ -24310,7 +24294,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="156" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A156" s="9" t="s">
         <v>383</v>
       </c>
@@ -24450,7 +24434,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="157" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
         <v>383</v>
       </c>
@@ -24500,7 +24484,7 @@
         <v>41.1</v>
       </c>
       <c r="Q157" s="32">
-        <v>9.6999999999999993</v>
+        <v>9.7</v>
       </c>
       <c r="R157" s="23">
         <v>652</v>
@@ -24590,7 +24574,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="158" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A158" s="9" t="s">
         <v>383</v>
       </c>
@@ -24730,7 +24714,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="159" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A159" s="17" t="s">
         <v>383</v>
       </c>
@@ -24870,7 +24854,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="160" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A160" s="9" t="s">
         <v>383</v>
       </c>
@@ -24911,7 +24895,7 @@
         <v>3</v>
       </c>
       <c r="N160" s="14">
-        <v>17.899999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="O160" s="14">
         <v>48.6</v>
@@ -24920,7 +24904,7 @@
         <v>28.5</v>
       </c>
       <c r="Q160" s="14">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="R160" s="15">
         <v>540</v>
@@ -25010,7 +24994,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="161" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A161" s="17" t="s">
         <v>393</v>
       </c>
@@ -25150,7 +25134,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="162" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
         <v>393</v>
       </c>
@@ -25200,7 +25184,7 @@
         <v>24.7</v>
       </c>
       <c r="Q162" s="14">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="R162" s="15">
         <v>573</v>
@@ -25290,7 +25274,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="163" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A163" s="17" t="s">
         <v>393</v>
       </c>
@@ -25430,7 +25414,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="164" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A164" s="9" t="s">
         <v>393</v>
       </c>
@@ -25471,7 +25455,7 @@
         <v>5</v>
       </c>
       <c r="N164" s="14">
-        <v>17.100000000000001</v>
+        <v>17.1</v>
       </c>
       <c r="O164" s="14">
         <v>41.9</v>
@@ -25480,7 +25464,7 @@
         <v>26.5</v>
       </c>
       <c r="Q164" s="14">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="R164" s="15">
         <v>538</v>
@@ -25570,7 +25554,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="165" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A165" s="17" t="s">
         <v>393</v>
       </c>
@@ -25611,7 +25595,7 @@
         <v>2</v>
       </c>
       <c r="N165" s="21">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="O165" s="21">
         <v>30.4</v>
@@ -25710,7 +25694,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="166" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A166" s="9" t="s">
         <v>393</v>
       </c>
@@ -25757,7 +25741,7 @@
         <v>80</v>
       </c>
       <c r="P166" s="14">
-        <v>17.399999999999999</v>
+        <v>17.4</v>
       </c>
       <c r="Q166" s="22">
         <v>5.9</v>
@@ -25850,7 +25834,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="167" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A167" s="17" t="s">
         <v>393</v>
       </c>
@@ -25900,7 +25884,7 @@
         <v>26.4</v>
       </c>
       <c r="Q167" s="21">
-        <v>8.8000000000000007</v>
+        <v>8.8</v>
       </c>
       <c r="R167" s="23">
         <v>467</v>
@@ -25990,7 +25974,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="168" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A168" s="9" t="s">
         <v>404</v>
       </c>
@@ -26019,7 +26003,7 @@
         <v>52</v>
       </c>
       <c r="J168" s="28">
-        <v>1.1399999999999999</v>
+        <v>1.14</v>
       </c>
       <c r="K168" s="10">
         <v>5</v>
@@ -26034,7 +26018,7 @@
         <v>9.1</v>
       </c>
       <c r="O168" s="14">
-        <v>34.799999999999997</v>
+        <v>34.8</v>
       </c>
       <c r="P168" s="14">
         <v>32.1</v>
@@ -26130,7 +26114,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="169" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A169" s="17" t="s">
         <v>404</v>
       </c>
@@ -26270,7 +26254,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="170" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A170" s="9" t="s">
         <v>404</v>
       </c>
@@ -26317,7 +26301,7 @@
         <v>46.2</v>
       </c>
       <c r="P170" s="14">
-        <v>33.799999999999997</v>
+        <v>33.8</v>
       </c>
       <c r="Q170" s="14">
         <v>7.8</v>
@@ -26410,7 +26394,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="171" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A171" s="17" t="s">
         <v>404</v>
       </c>
@@ -26550,7 +26534,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="172" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
         <v>404</v>
       </c>
@@ -26690,7 +26674,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="173" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A173" s="17" t="s">
         <v>404</v>
       </c>
@@ -26830,7 +26814,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="174" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A174" s="9" t="s">
         <v>404</v>
       </c>
@@ -26871,10 +26855,10 @@
         <v>11</v>
       </c>
       <c r="N174" s="14">
-        <v>18.600000000000001</v>
+        <v>18.6</v>
       </c>
       <c r="O174" s="14">
-        <v>73.099999999999994</v>
+        <v>73.1</v>
       </c>
       <c r="P174" s="14">
         <v>20.7</v>
@@ -26970,7 +26954,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="175" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A175" s="17" t="s">
         <v>404</v>
       </c>
@@ -27014,7 +26998,7 @@
         <v>10.1</v>
       </c>
       <c r="O175" s="21">
-        <v>34.799999999999997</v>
+        <v>34.8</v>
       </c>
       <c r="P175" s="21">
         <v>18</v>
@@ -27110,7 +27094,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="176" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A176" s="9" t="s">
         <v>404</v>
       </c>
@@ -27250,7 +27234,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="177" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A177" s="17" t="s">
         <v>425</v>
       </c>
@@ -27390,7 +27374,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="178" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
         <v>425</v>
       </c>
@@ -27530,7 +27514,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="179" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A179" s="17" t="s">
         <v>425</v>
       </c>
@@ -27670,7 +27654,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="180" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A180" s="9" t="s">
         <v>425</v>
       </c>
@@ -27810,7 +27794,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A181" s="17" t="s">
         <v>425</v>
       </c>
@@ -27950,7 +27934,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="182" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A182" s="9" t="s">
         <v>425</v>
       </c>
@@ -27997,7 +27981,7 @@
         <v>58</v>
       </c>
       <c r="P182" s="14">
-        <v>32.700000000000003</v>
+        <v>32.7</v>
       </c>
       <c r="Q182" s="14">
         <v>7.6</v>
@@ -28090,7 +28074,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="183" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A183" s="17" t="s">
         <v>425</v>
       </c>
@@ -28230,7 +28214,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="184" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A184" s="9" t="s">
         <v>437</v>
       </c>
@@ -28271,16 +28255,16 @@
         <v>15</v>
       </c>
       <c r="N184" s="14">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="O184" s="14">
         <v>69.8</v>
       </c>
       <c r="P184" s="14">
-        <v>34.200000000000003</v>
+        <v>34.2</v>
       </c>
       <c r="Q184" s="14">
-        <v>8.6999999999999993</v>
+        <v>8.7</v>
       </c>
       <c r="R184" s="15">
         <v>635</v>
@@ -28370,7 +28354,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="185" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A185" s="17" t="s">
         <v>437</v>
       </c>
@@ -28399,7 +28383,7 @@
         <v>52</v>
       </c>
       <c r="J185" s="25">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="K185" s="18">
         <v>8</v>
@@ -28510,7 +28494,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="186" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A186" s="9" t="s">
         <v>437</v>
       </c>
@@ -28650,7 +28634,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="187" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A187" s="17" t="s">
         <v>437</v>
       </c>
@@ -28790,7 +28774,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="188" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A188" s="9" t="s">
         <v>437</v>
       </c>
@@ -28930,7 +28914,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="189" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A189" s="17" t="s">
         <v>437</v>
       </c>
@@ -29070,7 +29054,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="190" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A190" s="9" t="s">
         <v>437</v>
       </c>
@@ -29210,7 +29194,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="191" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A191" s="17" t="s">
         <v>437</v>
       </c>
@@ -29350,7 +29334,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="192" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A192" s="9" t="s">
         <v>437</v>
       </c>
@@ -29394,7 +29378,7 @@
         <v>20.2</v>
       </c>
       <c r="O192" s="14">
-        <v>38.200000000000003</v>
+        <v>38.2</v>
       </c>
       <c r="P192" s="14">
         <v>18.8</v>
@@ -29490,7 +29474,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="193" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A193" s="17" t="s">
         <v>437</v>
       </c>
@@ -29519,7 +29503,7 @@
         <v>60</v>
       </c>
       <c r="J193" s="20">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="K193" s="18">
         <v>16</v>
@@ -29630,7 +29614,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="194" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A194" s="9" t="s">
         <v>437</v>
       </c>
@@ -29770,7 +29754,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="195" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A195" s="17" t="s">
         <v>437</v>
       </c>
@@ -29817,7 +29801,7 @@
         <v>25</v>
       </c>
       <c r="P195" s="21">
-        <v>16.600000000000001</v>
+        <v>16.6</v>
       </c>
       <c r="Q195" s="22">
         <v>6.4</v>
@@ -29910,7 +29894,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="196" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A196" s="9" t="s">
         <v>460</v>
       </c>
@@ -29957,7 +29941,7 @@
         <v>28.3</v>
       </c>
       <c r="P196" s="14">
-        <v>8.6999999999999993</v>
+        <v>8.7</v>
       </c>
       <c r="Q196" s="22">
         <v>3.9</v>
@@ -30050,7 +30034,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="197" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A197" s="17" t="s">
         <v>460</v>
       </c>
@@ -30091,7 +30075,7 @@
         <v>2</v>
       </c>
       <c r="N197" s="29">
-        <v>20.399999999999999</v>
+        <v>20.4</v>
       </c>
       <c r="O197" s="21">
         <v>35.4</v>
@@ -30190,7 +30174,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="198" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A198" s="9" t="s">
         <v>460</v>
       </c>
@@ -30330,7 +30314,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="199" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A199" s="17" t="s">
         <v>460</v>
       </c>
@@ -30470,7 +30454,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="200" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A200" s="9" t="s">
         <v>460</v>
       </c>
@@ -30520,7 +30504,7 @@
         <v>30.7</v>
       </c>
       <c r="Q200" s="22">
-        <v>4.9000000000000004</v>
+        <v>4.9</v>
       </c>
       <c r="R200" s="15">
         <v>407</v>
@@ -30610,7 +30594,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="201" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A201" s="17" t="s">
         <v>460</v>
       </c>
@@ -30750,7 +30734,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="202" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A202" s="9" t="s">
         <v>460</v>
       </c>
@@ -30890,7 +30874,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="203" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A203" s="17" t="s">
         <v>474</v>
       </c>
@@ -30937,7 +30921,7 @@
         <v>29.4</v>
       </c>
       <c r="P203" s="21">
-        <v>17.899999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="Q203" s="22">
         <v>6.5</v>
@@ -31030,7 +31014,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="204" spans="1:46" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" ht="20" customHeight="1" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A204" s="9" t="s">
         <v>474</v>
       </c>
@@ -31059,7 +31043,7 @@
         <v>60</v>
       </c>
       <c r="J204" s="28">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="K204" s="10">
         <v>3</v>
@@ -31171,16 +31155,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:AT1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="3" max="4" width="10" customWidth="1"/>
@@ -31194,86 +31178,86 @@
     <col min="18" max="18" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="51" t="s">
+    <row r="1" ht="28" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
         <v>478</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
     </row>
-    <row r="2" spans="1:18" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="34" t="s">
+    <row r="2" ht="26" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="35" t="s">
         <v>479</v>
       </c>
-      <c r="C2" s="34" t="s">
+      <c r="C2" s="35" t="s">
         <v>480</v>
       </c>
-      <c r="D2" s="34" t="s">
+      <c r="D2" s="35" t="s">
         <v>481</v>
       </c>
-      <c r="E2" s="34" t="s">
+      <c r="E2" s="35" t="s">
         <v>482</v>
       </c>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="35" t="s">
         <v>483</v>
       </c>
-      <c r="G2" s="34" t="s">
+      <c r="G2" s="35" t="s">
         <v>484</v>
       </c>
-      <c r="H2" s="34" t="s">
+      <c r="H2" s="35" t="s">
         <v>485</v>
       </c>
-      <c r="I2" s="34" t="s">
+      <c r="I2" s="35" t="s">
         <v>486</v>
       </c>
-      <c r="J2" s="34" t="s">
+      <c r="J2" s="35" t="s">
         <v>487</v>
       </c>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="35" t="s">
         <v>488</v>
       </c>
-      <c r="L2" s="34" t="s">
+      <c r="L2" s="35" t="s">
         <v>489</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="M2" s="35" t="s">
         <v>490</v>
       </c>
-      <c r="N2" s="34" t="s">
+      <c r="N2" s="35" t="s">
         <v>491</v>
       </c>
-      <c r="O2" s="34" t="s">
+      <c r="O2" s="35" t="s">
         <v>492</v>
       </c>
-      <c r="P2" s="34" t="s">
+      <c r="P2" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="Q2" s="34" t="s">
+      <c r="Q2" s="35" t="s">
         <v>51</v>
       </c>
-      <c r="R2" s="34" t="s">
+      <c r="R2" s="35" t="s">
         <v>493</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+    <row r="3" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
         <v>72</v>
       </c>
       <c r="B3" s="10">
@@ -31285,8 +31269,8 @@
       <c r="D3" s="10">
         <v>38</v>
       </c>
-      <c r="E3" s="36">
-        <v>0.51282051282051277</v>
+      <c r="E3" s="37">
+        <v>0.5128205128205128</v>
       </c>
       <c r="F3" s="31">
         <v>2.52</v>
@@ -31309,10 +31293,10 @@
       <c r="L3" s="15">
         <v>948</v>
       </c>
-      <c r="M3" s="37">
+      <c r="M3" s="38">
         <v>24.1</v>
       </c>
-      <c r="N3" s="37">
+      <c r="N3" s="38">
         <v>52.6</v>
       </c>
       <c r="O3" s="10">
@@ -31328,8 +31312,8 @@
         <v>494</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+    <row r="4" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" s="39" t="s">
         <v>49</v>
       </c>
       <c r="B4" s="18">
@@ -31341,11 +31325,11 @@
       <c r="D4" s="18">
         <v>13</v>
       </c>
-      <c r="E4" s="39">
-        <v>0.56666666666666665</v>
+      <c r="E4" s="40">
+        <v>0.5666666666666667</v>
       </c>
       <c r="F4" s="25">
-        <v>4.5599999999999996</v>
+        <v>4.56</v>
       </c>
       <c r="G4" s="18">
         <v>13.2</v>
@@ -31354,7 +31338,7 @@
         <v>7</v>
       </c>
       <c r="I4" s="18">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="J4" s="21">
         <v>7.7</v>
@@ -31365,10 +31349,10 @@
       <c r="L4" s="23">
         <v>1281</v>
       </c>
-      <c r="M4" s="40">
+      <c r="M4" s="41">
         <v>33.5</v>
       </c>
-      <c r="N4" s="40">
+      <c r="N4" s="41">
         <v>55</v>
       </c>
       <c r="O4" s="18">
@@ -31384,8 +31368,8 @@
         <v>495</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+    <row r="5" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>233</v>
       </c>
       <c r="B5" s="10">
@@ -31397,20 +31381,20 @@
       <c r="D5" s="10">
         <v>8</v>
       </c>
-      <c r="E5" s="41">
-        <v>0.27272727272727271</v>
+      <c r="E5" s="42">
+        <v>0.2727272727272727</v>
       </c>
       <c r="F5" s="31">
-        <v>2.5299999999999998</v>
+        <v>2.53</v>
       </c>
       <c r="G5" s="10">
-        <v>10.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="H5" s="13">
         <v>6.9</v>
       </c>
       <c r="I5" s="10">
-        <v>4.0999999999999996</v>
+        <v>4.1</v>
       </c>
       <c r="J5" s="22">
         <v>6.6</v>
@@ -31421,10 +31405,10 @@
       <c r="L5" s="15">
         <v>1286</v>
       </c>
-      <c r="M5" s="37">
+      <c r="M5" s="38">
         <v>42.4</v>
       </c>
-      <c r="N5" s="37">
+      <c r="N5" s="38">
         <v>51.5</v>
       </c>
       <c r="O5" s="10">
@@ -31440,8 +31424,8 @@
         <v>496</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38" t="s">
+    <row r="6" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A6" s="39" t="s">
         <v>109</v>
       </c>
       <c r="B6" s="18">
@@ -31453,8 +31437,8 @@
       <c r="D6" s="18">
         <v>4</v>
       </c>
-      <c r="E6" s="39">
-        <v>0.63636363636363635</v>
+      <c r="E6" s="40">
+        <v>0.6363636363636364</v>
       </c>
       <c r="F6" s="25">
         <v>4.34</v>
@@ -31477,10 +31461,10 @@
       <c r="L6" s="23">
         <v>1317</v>
       </c>
-      <c r="M6" s="40">
-        <v>35.299999999999997</v>
-      </c>
-      <c r="N6" s="40">
+      <c r="M6" s="41">
+        <v>35.3</v>
+      </c>
+      <c r="N6" s="41">
         <v>63.7</v>
       </c>
       <c r="O6" s="18">
@@ -31496,8 +31480,8 @@
         <v>497</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
+    <row r="7" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
         <v>354</v>
       </c>
       <c r="B7" s="10">
@@ -31509,7 +31493,7 @@
       <c r="D7" s="10">
         <v>2</v>
       </c>
-      <c r="E7" s="39">
+      <c r="E7" s="40">
         <v>0.8</v>
       </c>
       <c r="F7" s="25">
@@ -31525,7 +31509,7 @@
         <v>9</v>
       </c>
       <c r="J7" s="14">
-        <v>8.1999999999999993</v>
+        <v>8.2</v>
       </c>
       <c r="K7" s="15">
         <v>573</v>
@@ -31533,10 +31517,10 @@
       <c r="L7" s="15">
         <v>1188</v>
       </c>
-      <c r="M7" s="37">
+      <c r="M7" s="38">
         <v>28.5</v>
       </c>
-      <c r="N7" s="37">
+      <c r="N7" s="38">
         <v>52.8</v>
       </c>
       <c r="O7" s="10">
@@ -31552,8 +31536,8 @@
         <v>498</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="38" t="s">
+    <row r="8" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A8" s="39" t="s">
         <v>63</v>
       </c>
       <c r="B8" s="18">
@@ -31565,8 +31549,8 @@
       <c r="D8" s="18">
         <v>1</v>
       </c>
-      <c r="E8" s="39">
-        <v>0.88888888888888884</v>
+      <c r="E8" s="40">
+        <v>0.8888888888888888</v>
       </c>
       <c r="F8" s="25">
         <v>6.96</v>
@@ -31589,10 +31573,10 @@
       <c r="L8" s="23">
         <v>1601</v>
       </c>
-      <c r="M8" s="40">
+      <c r="M8" s="41">
         <v>36.6</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N8" s="41">
         <v>63</v>
       </c>
       <c r="O8" s="18">
@@ -31608,8 +31592,8 @@
         <v>499</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+    <row r="9" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
         <v>87</v>
       </c>
       <c r="B9" s="10">
@@ -31621,8 +31605,8 @@
       <c r="D9" s="10">
         <v>4</v>
       </c>
-      <c r="E9" s="41">
-        <v>0.33333333333333331</v>
+      <c r="E9" s="42">
+        <v>0.3333333333333333</v>
       </c>
       <c r="F9" s="31">
         <v>3.28</v>
@@ -31645,10 +31629,10 @@
       <c r="L9" s="15">
         <v>1022</v>
       </c>
-      <c r="M9" s="37">
+      <c r="M9" s="38">
         <v>29.1</v>
       </c>
-      <c r="N9" s="37">
+      <c r="N9" s="38">
         <v>50.7</v>
       </c>
       <c r="O9" s="10">
@@ -31664,8 +31648,8 @@
         <v>320</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="38" t="s">
+    <row r="10" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
         <v>352</v>
       </c>
       <c r="B10" s="18">
@@ -31677,7 +31661,7 @@
       <c r="D10" s="18">
         <v>2</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="43">
         <v>0.5</v>
       </c>
       <c r="F10" s="31">
@@ -31687,7 +31671,7 @@
         <v>6.5</v>
       </c>
       <c r="H10" s="13">
-        <v>8.3000000000000007</v>
+        <v>8.3</v>
       </c>
       <c r="I10" s="18">
         <v>16.5</v>
@@ -31701,10 +31685,10 @@
       <c r="L10" s="23">
         <v>783</v>
       </c>
-      <c r="M10" s="40">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="N10" s="40">
+      <c r="M10" s="41">
+        <v>18.1</v>
+      </c>
+      <c r="N10" s="41">
         <v>58.4</v>
       </c>
       <c r="O10" s="18">
@@ -31720,8 +31704,8 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+    <row r="11" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
         <v>98</v>
       </c>
       <c r="B11" s="10">
@@ -31733,7 +31717,7 @@
       <c r="D11" s="10">
         <v>3</v>
       </c>
-      <c r="E11" s="41">
+      <c r="E11" s="42">
         <v>0.25</v>
       </c>
       <c r="F11" s="12">
@@ -31757,10 +31741,10 @@
       <c r="L11" s="15">
         <v>937</v>
       </c>
-      <c r="M11" s="37">
+      <c r="M11" s="38">
         <v>26.3</v>
       </c>
-      <c r="N11" s="37">
+      <c r="N11" s="38">
         <v>57.2</v>
       </c>
       <c r="O11" s="10">
@@ -31776,8 +31760,8 @@
         <v>501</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
+    <row r="12" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" s="39" t="s">
         <v>218</v>
       </c>
       <c r="B12" s="18">
@@ -31789,14 +31773,14 @@
       <c r="D12" s="18">
         <v>3</v>
       </c>
-      <c r="E12" s="41">
+      <c r="E12" s="42">
         <v>0</v>
       </c>
       <c r="F12" s="28">
         <v>1.06</v>
       </c>
       <c r="G12" s="18">
-        <v>8.6999999999999993</v>
+        <v>8.7</v>
       </c>
       <c r="H12" s="13">
         <v>12.7</v>
@@ -31813,10 +31797,10 @@
       <c r="L12" s="23">
         <v>1016</v>
       </c>
-      <c r="M12" s="40">
+      <c r="M12" s="41">
         <v>28.3</v>
       </c>
-      <c r="N12" s="40">
+      <c r="N12" s="41">
         <v>48.2</v>
       </c>
       <c r="O12" s="18">
@@ -31832,8 +31816,8 @@
         <v>271</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
+    <row r="13" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
         <v>140</v>
       </c>
       <c r="B13" s="10">
@@ -31845,8 +31829,8 @@
       <c r="D13" s="10">
         <v>2</v>
       </c>
-      <c r="E13" s="41">
-        <v>0.33333333333333331</v>
+      <c r="E13" s="42">
+        <v>0.3333333333333333</v>
       </c>
       <c r="F13" s="28">
         <v>0.48</v>
@@ -31858,7 +31842,7 @@
         <v>12</v>
       </c>
       <c r="I13" s="10">
-        <v>2.2999999999999998</v>
+        <v>2.3</v>
       </c>
       <c r="J13" s="22">
         <v>5.7</v>
@@ -31869,10 +31853,10 @@
       <c r="L13" s="15">
         <v>632</v>
       </c>
-      <c r="M13" s="37">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="N13" s="37">
+      <c r="M13" s="38">
+        <v>17.4</v>
+      </c>
+      <c r="N13" s="38">
         <v>24.7</v>
       </c>
       <c r="O13" s="10">
@@ -31888,8 +31872,8 @@
         <v>498</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+    <row r="14" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" s="39" t="s">
         <v>165</v>
       </c>
       <c r="B14" s="18">
@@ -31901,7 +31885,7 @@
       <c r="D14" s="18">
         <v>0</v>
       </c>
-      <c r="E14" s="39">
+      <c r="E14" s="40">
         <v>1</v>
       </c>
       <c r="F14" s="31">
@@ -31914,10 +31898,10 @@
         <v>5</v>
       </c>
       <c r="I14" s="18">
-        <v>9.3000000000000007</v>
+        <v>9.3</v>
       </c>
       <c r="J14" s="22">
-        <v>1.1000000000000001</v>
+        <v>1.1</v>
       </c>
       <c r="K14" s="23">
         <v>358</v>
@@ -31925,10 +31909,10 @@
       <c r="L14" s="23">
         <v>767</v>
       </c>
-      <c r="M14" s="40">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="N14" s="40">
+      <c r="M14" s="41">
+        <v>18.6</v>
+      </c>
+      <c r="N14" s="41">
         <v>42.1</v>
       </c>
       <c r="O14" s="18">
@@ -31944,8 +31928,8 @@
         <v>502</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+    <row r="15" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
         <v>463</v>
       </c>
       <c r="B15" s="10">
@@ -31957,7 +31941,7 @@
       <c r="D15" s="10">
         <v>0</v>
       </c>
-      <c r="E15" s="39">
+      <c r="E15" s="40">
         <v>1</v>
       </c>
       <c r="F15" s="28">
@@ -31981,10 +31965,10 @@
       <c r="L15" s="15">
         <v>465</v>
       </c>
-      <c r="M15" s="37">
+      <c r="M15" s="38">
         <v>10.9</v>
       </c>
-      <c r="N15" s="37">
+      <c r="N15" s="38">
         <v>36.1</v>
       </c>
       <c r="O15" s="10">
@@ -32000,8 +31984,8 @@
         <v>503</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="38" t="s">
+    <row r="16" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
         <v>459</v>
       </c>
       <c r="B16" s="18">
@@ -32013,7 +31997,7 @@
       <c r="D16" s="18">
         <v>2</v>
       </c>
-      <c r="E16" s="41">
+      <c r="E16" s="42">
         <v>0</v>
       </c>
       <c r="F16" s="28">
@@ -32037,10 +32021,10 @@
       <c r="L16" s="23">
         <v>637</v>
       </c>
-      <c r="M16" s="40">
+      <c r="M16" s="41">
         <v>17.3</v>
       </c>
-      <c r="N16" s="40">
+      <c r="N16" s="41">
         <v>27.2</v>
       </c>
       <c r="O16" s="18">
@@ -32056,8 +32040,8 @@
         <v>125</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
+    <row r="17" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
         <v>253</v>
       </c>
       <c r="B17" s="10">
@@ -32069,7 +32053,7 @@
       <c r="D17" s="10">
         <v>0</v>
       </c>
-      <c r="E17" s="39">
+      <c r="E17" s="40">
         <v>1</v>
       </c>
       <c r="F17" s="12">
@@ -32093,10 +32077,10 @@
       <c r="L17" s="15">
         <v>1369</v>
       </c>
-      <c r="M17" s="37">
+      <c r="M17" s="38">
         <v>30.5</v>
       </c>
-      <c r="N17" s="37">
+      <c r="N17" s="38">
         <v>50.6</v>
       </c>
       <c r="O17" s="10">
@@ -32112,8 +32096,8 @@
         <v>504</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
+    <row r="18" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A18" s="39" t="s">
         <v>174</v>
       </c>
       <c r="B18" s="18">
@@ -32125,7 +32109,7 @@
       <c r="D18" s="18">
         <v>1</v>
       </c>
-      <c r="E18" s="42">
+      <c r="E18" s="43">
         <v>0.5</v>
       </c>
       <c r="F18" s="31">
@@ -32149,10 +32133,10 @@
       <c r="L18" s="23">
         <v>719</v>
       </c>
-      <c r="M18" s="40">
+      <c r="M18" s="41">
         <v>20.2</v>
       </c>
-      <c r="N18" s="40">
+      <c r="N18" s="41">
         <v>58.3</v>
       </c>
       <c r="O18" s="18">
@@ -32168,8 +32152,8 @@
         <v>505</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
+    <row r="19" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
         <v>207</v>
       </c>
       <c r="B19" s="10">
@@ -32181,7 +32165,7 @@
       <c r="D19" s="10">
         <v>2</v>
       </c>
-      <c r="E19" s="41">
+      <c r="E19" s="42">
         <v>0</v>
       </c>
       <c r="F19" s="28">
@@ -32205,10 +32189,10 @@
       <c r="L19" s="15">
         <v>691</v>
       </c>
-      <c r="M19" s="37">
+      <c r="M19" s="38">
         <v>23.4</v>
       </c>
-      <c r="N19" s="37">
+      <c r="N19" s="38">
         <v>42.8</v>
       </c>
       <c r="O19" s="10">
@@ -32224,8 +32208,8 @@
         <v>506</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38" t="s">
+    <row r="20" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A20" s="39" t="s">
         <v>326</v>
       </c>
       <c r="B20" s="18">
@@ -32237,7 +32221,7 @@
       <c r="D20" s="18">
         <v>2</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="42">
         <v>0</v>
       </c>
       <c r="F20" s="28">
@@ -32261,11 +32245,11 @@
       <c r="L20" s="23">
         <v>435</v>
       </c>
-      <c r="M20" s="40">
+      <c r="M20" s="41">
         <v>19.8</v>
       </c>
-      <c r="N20" s="40">
-        <v>66.900000000000006</v>
+      <c r="N20" s="41">
+        <v>66.9</v>
       </c>
       <c r="O20" s="18">
         <v>8</v>
@@ -32280,8 +32264,8 @@
         <v>257</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
+    <row r="21" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A21" s="36" t="s">
         <v>159</v>
       </c>
       <c r="B21" s="10">
@@ -32293,7 +32277,7 @@
       <c r="D21" s="10">
         <v>1</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="37">
         <v>0.5</v>
       </c>
       <c r="F21" s="12">
@@ -32317,10 +32301,10 @@
       <c r="L21" s="15">
         <v>771</v>
       </c>
-      <c r="M21" s="37">
+      <c r="M21" s="38">
         <v>21.6</v>
       </c>
-      <c r="N21" s="37">
+      <c r="N21" s="38">
         <v>60.5</v>
       </c>
       <c r="O21" s="10">
@@ -32336,8 +32320,8 @@
         <v>351</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="38" t="s">
+    <row r="22" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A22" s="39" t="s">
         <v>473</v>
       </c>
       <c r="B22" s="18">
@@ -32349,7 +32333,7 @@
       <c r="D22" s="18">
         <v>1</v>
       </c>
-      <c r="E22" s="41">
+      <c r="E22" s="42">
         <v>0</v>
       </c>
       <c r="F22" s="28">
@@ -32373,10 +32357,10 @@
       <c r="L22" s="23">
         <v>552</v>
       </c>
-      <c r="M22" s="40">
+      <c r="M22" s="41">
         <v>12</v>
       </c>
-      <c r="N22" s="40">
+      <c r="N22" s="41">
         <v>14.7</v>
       </c>
       <c r="O22" s="18">
@@ -32392,8 +32376,8 @@
         <v>472</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="35" t="s">
+    <row r="23" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="36" t="s">
         <v>454</v>
       </c>
       <c r="B23" s="10">
@@ -32405,7 +32389,7 @@
       <c r="D23" s="10">
         <v>1</v>
       </c>
-      <c r="E23" s="41">
+      <c r="E23" s="42">
         <v>0</v>
       </c>
       <c r="F23" s="28">
@@ -32429,11 +32413,11 @@
       <c r="L23" s="15">
         <v>679</v>
       </c>
-      <c r="M23" s="37">
+      <c r="M23" s="38">
         <v>18.8</v>
       </c>
-      <c r="N23" s="37">
-        <v>38.200000000000003</v>
+      <c r="N23" s="38">
+        <v>38.2</v>
       </c>
       <c r="O23" s="10">
         <v>13</v>
@@ -32448,8 +32432,8 @@
         <v>453</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="38" t="s">
+    <row r="24" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A24" s="39" t="s">
         <v>441</v>
       </c>
       <c r="B24" s="18">
@@ -32461,11 +32445,11 @@
       <c r="D24" s="18">
         <v>1</v>
       </c>
-      <c r="E24" s="41">
+      <c r="E24" s="42">
         <v>0</v>
       </c>
       <c r="F24" s="25">
-        <v>4.5999999999999996</v>
+        <v>4.6</v>
       </c>
       <c r="G24" s="18">
         <v>8</v>
@@ -32485,10 +32469,10 @@
       <c r="L24" s="23">
         <v>988</v>
       </c>
-      <c r="M24" s="40">
+      <c r="M24" s="41">
         <v>24.5</v>
       </c>
-      <c r="N24" s="40">
+      <c r="N24" s="41">
         <v>62.2</v>
       </c>
       <c r="O24" s="18">
@@ -32504,8 +32488,8 @@
         <v>440</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="35" t="s">
+    <row r="25" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A25" s="36" t="s">
         <v>422</v>
       </c>
       <c r="B25" s="10">
@@ -32517,7 +32501,7 @@
       <c r="D25" s="10">
         <v>0</v>
       </c>
-      <c r="E25" s="39">
+      <c r="E25" s="40">
         <v>1</v>
       </c>
       <c r="F25" s="12">
@@ -32541,11 +32525,11 @@
       <c r="L25" s="15">
         <v>477</v>
       </c>
-      <c r="M25" s="37">
+      <c r="M25" s="38">
         <v>18</v>
       </c>
-      <c r="N25" s="37">
-        <v>34.799999999999997</v>
+      <c r="N25" s="38">
+        <v>34.8</v>
       </c>
       <c r="O25" s="10">
         <v>12</v>
@@ -32560,8 +32544,8 @@
         <v>421</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="38" t="s">
+    <row r="26" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A26" s="39" t="s">
         <v>419</v>
       </c>
       <c r="B26" s="18">
@@ -32573,7 +32557,7 @@
       <c r="D26" s="18">
         <v>1</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="42">
         <v>0</v>
       </c>
       <c r="F26" s="20">
@@ -32597,11 +32581,11 @@
       <c r="L26" s="23">
         <v>720</v>
       </c>
-      <c r="M26" s="40">
+      <c r="M26" s="41">
         <v>20.7</v>
       </c>
-      <c r="N26" s="40">
-        <v>73.099999999999994</v>
+      <c r="N26" s="41">
+        <v>73.1</v>
       </c>
       <c r="O26" s="18">
         <v>20</v>
@@ -32616,8 +32600,8 @@
         <v>418</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="35" t="s">
+    <row r="27" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A27" s="36" t="s">
         <v>416</v>
       </c>
       <c r="B27" s="10">
@@ -32629,7 +32613,7 @@
       <c r="D27" s="10">
         <v>1</v>
       </c>
-      <c r="E27" s="41">
+      <c r="E27" s="42">
         <v>0</v>
       </c>
       <c r="F27" s="12">
@@ -32653,10 +32637,10 @@
       <c r="L27" s="15">
         <v>915</v>
       </c>
-      <c r="M27" s="37">
+      <c r="M27" s="38">
         <v>27.4</v>
       </c>
-      <c r="N27" s="37">
+      <c r="N27" s="38">
         <v>56.7</v>
       </c>
       <c r="O27" s="10">
@@ -32672,8 +32656,8 @@
         <v>415</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="38" t="s">
+    <row r="28" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A28" s="39" t="s">
         <v>396</v>
       </c>
       <c r="B28" s="18">
@@ -32685,7 +32669,7 @@
       <c r="D28" s="18">
         <v>0</v>
       </c>
-      <c r="E28" s="39">
+      <c r="E28" s="40">
         <v>1</v>
       </c>
       <c r="F28" s="25">
@@ -32709,10 +32693,10 @@
       <c r="L28" s="23">
         <v>1857</v>
       </c>
-      <c r="M28" s="40">
+      <c r="M28" s="41">
         <v>40</v>
       </c>
-      <c r="N28" s="40">
+      <c r="N28" s="41">
         <v>71.8</v>
       </c>
       <c r="O28" s="18">
@@ -32728,8 +32712,8 @@
         <v>395</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="35" t="s">
+    <row r="29" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A29" s="36" t="s">
         <v>369</v>
       </c>
       <c r="B29" s="10">
@@ -32741,7 +32725,7 @@
       <c r="D29" s="10">
         <v>1</v>
       </c>
-      <c r="E29" s="41">
+      <c r="E29" s="42">
         <v>0</v>
       </c>
       <c r="F29" s="28">
@@ -32765,10 +32749,10 @@
       <c r="L29" s="15">
         <v>647</v>
       </c>
-      <c r="M29" s="37">
+      <c r="M29" s="38">
         <v>22.6</v>
       </c>
-      <c r="N29" s="37">
+      <c r="N29" s="38">
         <v>61.5</v>
       </c>
       <c r="O29" s="10">
@@ -32784,8 +32768,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="38" t="s">
+    <row r="30" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A30" s="39" t="s">
         <v>360</v>
       </c>
       <c r="B30" s="18">
@@ -32797,11 +32781,11 @@
       <c r="D30" s="18">
         <v>1</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="42">
         <v>0</v>
       </c>
       <c r="F30" s="28">
-        <v>1.1100000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="G30" s="18">
         <v>3</v>
@@ -32821,10 +32805,10 @@
       <c r="L30" s="23">
         <v>581</v>
       </c>
-      <c r="M30" s="40">
+      <c r="M30" s="41">
         <v>12.9</v>
       </c>
-      <c r="N30" s="40">
+      <c r="N30" s="41">
         <v>37</v>
       </c>
       <c r="O30" s="18">
@@ -32840,8 +32824,8 @@
         <v>359</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="35" t="s">
+    <row r="31" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A31" s="36" t="s">
         <v>357</v>
       </c>
       <c r="B31" s="10">
@@ -32853,7 +32837,7 @@
       <c r="D31" s="10">
         <v>1</v>
       </c>
-      <c r="E31" s="41">
+      <c r="E31" s="42">
         <v>0</v>
       </c>
       <c r="F31" s="28">
@@ -32877,10 +32861,10 @@
       <c r="L31" s="15">
         <v>628</v>
       </c>
-      <c r="M31" s="37">
+      <c r="M31" s="38">
         <v>23</v>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="38">
         <v>21.1</v>
       </c>
       <c r="O31" s="10">
@@ -32896,8 +32880,8 @@
         <v>356</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="38" t="s">
+    <row r="32" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A32" s="39" t="s">
         <v>209</v>
       </c>
       <c r="B32" s="18">
@@ -32909,7 +32893,7 @@
       <c r="D32" s="18">
         <v>0</v>
       </c>
-      <c r="E32" s="39">
+      <c r="E32" s="40">
         <v>1</v>
       </c>
       <c r="F32" s="25">
@@ -32925,7 +32909,7 @@
         <v>3</v>
       </c>
       <c r="J32" s="32">
-        <v>10.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="K32" s="23">
         <v>673</v>
@@ -32933,10 +32917,10 @@
       <c r="L32" s="23">
         <v>1536</v>
       </c>
-      <c r="M32" s="40">
-        <v>39.200000000000003</v>
-      </c>
-      <c r="N32" s="40">
+      <c r="M32" s="41">
+        <v>39.2</v>
+      </c>
+      <c r="N32" s="41">
         <v>55.6</v>
       </c>
       <c r="O32" s="18">
@@ -32952,8 +32936,8 @@
         <v>208</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="35" t="s">
+    <row r="33" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A33" s="36" t="s">
         <v>183</v>
       </c>
       <c r="B33" s="10">
@@ -32965,7 +32949,7 @@
       <c r="D33" s="10">
         <v>1</v>
       </c>
-      <c r="E33" s="41">
+      <c r="E33" s="42">
         <v>0</v>
       </c>
       <c r="F33" s="31">
@@ -32989,10 +32973,10 @@
       <c r="L33" s="15">
         <v>905</v>
       </c>
-      <c r="M33" s="37">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="N33" s="37">
+      <c r="M33" s="38">
+        <v>19.9</v>
+      </c>
+      <c r="N33" s="38">
         <v>75</v>
       </c>
       <c r="O33" s="10">
@@ -33008,8 +32992,8 @@
         <v>182</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="38" t="s">
+    <row r="34" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A34" s="39" t="s">
         <v>162</v>
       </c>
       <c r="B34" s="18">
@@ -33021,7 +33005,7 @@
       <c r="D34" s="18">
         <v>1</v>
       </c>
-      <c r="E34" s="41">
+      <c r="E34" s="42">
         <v>0</v>
       </c>
       <c r="F34" s="28">
@@ -33045,10 +33029,10 @@
       <c r="L34" s="23">
         <v>486</v>
       </c>
-      <c r="M34" s="40">
+      <c r="M34" s="41">
         <v>15.6</v>
       </c>
-      <c r="N34" s="40">
+      <c r="N34" s="41">
         <v>42.1</v>
       </c>
       <c r="O34" s="18">
@@ -33064,8 +33048,8 @@
         <v>161</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="35" t="s">
+    <row r="35" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A35" s="36" t="s">
         <v>153</v>
       </c>
       <c r="B35" s="10">
@@ -33077,7 +33061,7 @@
       <c r="D35" s="10">
         <v>1</v>
       </c>
-      <c r="E35" s="41">
+      <c r="E35" s="42">
         <v>0</v>
       </c>
       <c r="F35" s="28">
@@ -33101,10 +33085,10 @@
       <c r="L35" s="15">
         <v>1133</v>
       </c>
-      <c r="M35" s="37">
+      <c r="M35" s="38">
         <v>29.7</v>
       </c>
-      <c r="N35" s="37">
+      <c r="N35" s="38">
         <v>40</v>
       </c>
       <c r="O35" s="10">
@@ -33120,8 +33104,8 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="38" t="s">
+    <row r="36" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A36" s="39" t="s">
         <v>143</v>
       </c>
       <c r="B36" s="18">
@@ -33133,7 +33117,7 @@
       <c r="D36" s="18">
         <v>1</v>
       </c>
-      <c r="E36" s="41">
+      <c r="E36" s="42">
         <v>0</v>
       </c>
       <c r="F36" s="28">
@@ -33157,10 +33141,10 @@
       <c r="L36" s="23">
         <v>616</v>
       </c>
-      <c r="M36" s="40">
+      <c r="M36" s="41">
         <v>13.6</v>
       </c>
-      <c r="N36" s="40">
+      <c r="N36" s="41">
         <v>15.9</v>
       </c>
       <c r="O36" s="18">
@@ -33176,8 +33160,8 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="35" t="s">
+    <row r="37" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A37" s="36" t="s">
         <v>114</v>
       </c>
       <c r="B37" s="10">
@@ -33189,7 +33173,7 @@
       <c r="D37" s="10">
         <v>1</v>
       </c>
-      <c r="E37" s="41">
+      <c r="E37" s="42">
         <v>0</v>
       </c>
       <c r="F37" s="28">
@@ -33213,10 +33197,10 @@
       <c r="L37" s="15">
         <v>1185</v>
       </c>
-      <c r="M37" s="37">
+      <c r="M37" s="38">
         <v>21.5</v>
       </c>
-      <c r="N37" s="37">
+      <c r="N37" s="38">
         <v>30.8</v>
       </c>
       <c r="O37" s="10">
@@ -33232,8 +33216,8 @@
         <v>113</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="38" t="s">
+    <row r="38" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A38" s="39" t="s">
         <v>67</v>
       </c>
       <c r="B38" s="18">
@@ -33245,7 +33229,7 @@
       <c r="D38" s="18">
         <v>1</v>
       </c>
-      <c r="E38" s="41">
+      <c r="E38" s="42">
         <v>0</v>
       </c>
       <c r="F38" s="28">
@@ -33269,10 +33253,10 @@
       <c r="L38" s="23">
         <v>1281</v>
       </c>
-      <c r="M38" s="40">
+      <c r="M38" s="41">
         <v>28.8</v>
       </c>
-      <c r="N38" s="40">
+      <c r="N38" s="41">
         <v>52.5</v>
       </c>
       <c r="O38" s="18">
@@ -33289,56 +33273,56 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:R2" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A2:R2"/>
   <mergeCells count="1">
     <mergeCell ref="A1:R1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="52" t="s">
+    <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
         <v>507</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
     </row>
-    <row r="2" spans="1:6" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
+    <row r="2" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="45" t="s">
         <v>508</v>
       </c>
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="45" t="s">
         <v>509</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="45" t="s">
         <v>510</v>
       </c>
-      <c r="D2" s="43" t="s">
+      <c r="D2" s="45" t="s">
         <v>511</v>
       </c>
-      <c r="E2" s="43" t="s">
+      <c r="E2" s="45" t="s">
         <v>512</v>
       </c>
-      <c r="F2" s="43" t="s">
+      <c r="F2" s="45" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+    <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
         <v>479</v>
       </c>
       <c r="B3" s="10">
@@ -33357,8 +33341,8 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+    <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="39" t="s">
         <v>480</v>
       </c>
       <c r="B4" s="18">
@@ -33377,8 +33361,8 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="35" t="s">
+    <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
         <v>481</v>
       </c>
       <c r="B5" s="10">
@@ -33397,28 +33381,28 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38" t="s">
+    <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="39" t="s">
         <v>482</v>
       </c>
-      <c r="B6" s="41">
+      <c r="B6" s="42">
         <v>0.5</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="42">
         <v>0.5</v>
       </c>
-      <c r="D6" s="41">
+      <c r="D6" s="42">
         <v>0.5</v>
       </c>
-      <c r="E6" s="41">
+      <c r="E6" s="42">
         <v>0.5</v>
       </c>
-      <c r="F6" s="41">
+      <c r="F6" s="42">
         <v>0.5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="35" t="s">
+    <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
         <v>514</v>
       </c>
       <c r="B7" s="31">
@@ -33437,12 +33421,12 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="38" t="s">
+    <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="39" t="s">
         <v>515</v>
       </c>
       <c r="B8" s="18">
-        <v>9.8000000000000007</v>
+        <v>9.8</v>
       </c>
       <c r="C8" s="18">
         <v>10.6</v>
@@ -33451,18 +33435,18 @@
         <v>11.4</v>
       </c>
       <c r="E8" s="18">
-        <v>8.6999999999999993</v>
+        <v>8.7</v>
       </c>
       <c r="F8" s="18">
         <v>11.9</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="35" t="s">
+    <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
         <v>516</v>
       </c>
       <c r="B9" s="10">
-        <v>8.6999999999999993</v>
+        <v>8.7</v>
       </c>
       <c r="C9" s="10">
         <v>7.5</v>
@@ -33477,8 +33461,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="38" t="s">
+    <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="39" t="s">
         <v>517</v>
       </c>
       <c r="B10" s="18">
@@ -33497,8 +33481,8 @@
         <v>5.4</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="35" t="s">
+    <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
         <v>518</v>
       </c>
       <c r="B11" s="10">
@@ -33517,8 +33501,8 @@
         <v>7.4</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
+    <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="39" t="s">
         <v>519</v>
       </c>
       <c r="B12" s="18">
@@ -33537,8 +33521,8 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="35" t="s">
+    <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
         <v>520</v>
       </c>
       <c r="B13" s="10">
@@ -33557,8 +33541,8 @@
         <v>521</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+    <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="39" t="s">
         <v>521</v>
       </c>
       <c r="B14" s="18">
@@ -33577,8 +33561,8 @@
         <v>31.4</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="35" t="s">
+    <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
         <v>522</v>
       </c>
       <c r="B15" s="10">
@@ -33597,8 +33581,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="38" t="s">
+    <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="39" t="s">
         <v>523</v>
       </c>
       <c r="B16" s="18">
@@ -33608,7 +33592,7 @@
         <v>19.5</v>
       </c>
       <c r="D16" s="18">
-        <v>19.600000000000001</v>
+        <v>19.6</v>
       </c>
       <c r="E16" s="18">
         <v>19.5</v>
@@ -33617,8 +33601,8 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="35" t="s">
+    <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
         <v>524</v>
       </c>
       <c r="B17" s="10">
@@ -33637,8 +33621,8 @@
         <v>567</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
+    <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="39" t="s">
         <v>525</v>
       </c>
       <c r="B18" s="18">
@@ -33657,8 +33641,8 @@
         <v>10.9</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="35" t="s">
+    <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
         <v>526</v>
       </c>
       <c r="B19" s="10">
@@ -33677,8 +33661,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38" t="s">
+    <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="39" t="s">
         <v>527</v>
       </c>
       <c r="B20" s="18">
@@ -33702,14 +33686,14 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -33717,213 +33701,213 @@
     <col min="8" max="8" width="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+    <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="46" t="s">
         <v>528</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
     </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="44" t="s">
+    <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="47" t="s">
         <v>529</v>
       </c>
       <c r="B2" s="10">
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="45" t="s">
+    <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="48" t="s">
         <v>530</v>
       </c>
-      <c r="B3" s="42">
-        <v>0.49753694581280788</v>
+      <c r="B3" s="43">
+        <v>0.4975369458128079</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="44" t="s">
+    <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="47" t="s">
         <v>531</v>
       </c>
       <c r="B4" s="10" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="45" t="s">
+    <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="48" t="s">
         <v>533</v>
       </c>
       <c r="B5" s="18" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="44" t="s">
+    <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="47" t="s">
         <v>535</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="45" t="s">
+    <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="48" t="s">
         <v>537</v>
       </c>
       <c r="B7" s="18">
         <v>1049</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="44" t="s">
+    <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="47" t="s">
         <v>538</v>
       </c>
       <c r="B8" s="10">
         <v>492</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="45" t="s">
+    <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="48" t="s">
         <v>539</v>
       </c>
       <c r="B9" s="18" t="s">
         <v>540</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="44" t="s">
+    <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="47" t="s">
         <v>541</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="45" t="s">
+    <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="48" t="s">
         <v>543</v>
       </c>
       <c r="B11" s="18" t="s">
         <v>544</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="53" t="s">
+    <row r="13" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="46" t="s">
         <v>545</v>
       </c>
-      <c r="B13" s="53"/>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
+      <c r="B13" s="46"/>
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
     </row>
-    <row r="14" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="44" t="s">
+    <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="47" t="s">
         <v>546</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="45" t="s">
+    <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="48" t="s">
         <v>548</v>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="43">
         <v>0.4</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="44" t="s">
+    <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="47" t="s">
         <v>530</v>
       </c>
-      <c r="B16" s="36">
-        <v>0.49753694581280788</v>
+      <c r="B16" s="37">
+        <v>0.4975369458128079</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="45" t="s">
+    <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="48" t="s">
         <v>549</v>
       </c>
       <c r="B17" s="18" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="44" t="s">
+    <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="47" t="s">
         <v>551</v>
       </c>
       <c r="B18" s="10" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="45" t="s">
+    <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="48" t="s">
         <v>553</v>
       </c>
       <c r="B19" s="18" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="44" t="s">
+    <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="47" t="s">
         <v>555</v>
       </c>
       <c r="B20" s="10">
         <v>1241</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
+    <row r="22" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="46" t="s">
         <v>556</v>
       </c>
-      <c r="B22" s="53"/>
-      <c r="C22" s="53"/>
-      <c r="D22" s="53"/>
-      <c r="E22" s="53"/>
-      <c r="F22" s="53"/>
-      <c r="G22" s="53"/>
-      <c r="H22" s="53"/>
+      <c r="B22" s="46"/>
+      <c r="C22" s="46"/>
+      <c r="D22" s="46"/>
+      <c r="E22" s="46"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
+      <c r="H22" s="46"/>
     </row>
-    <row r="23" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="46" t="s">
+    <row r="23" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="49" t="s">
         <v>557</v>
       </c>
-      <c r="B23" s="46" t="s">
+      <c r="B23" s="49" t="s">
         <v>558</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="49" t="s">
         <v>559</v>
       </c>
-      <c r="D23" s="46" t="s">
+      <c r="D23" s="49" t="s">
         <v>483</v>
       </c>
-      <c r="E23" s="46" t="s">
+      <c r="E23" s="49" t="s">
         <v>484</v>
       </c>
-      <c r="F23" s="46" t="s">
+      <c r="F23" s="49" t="s">
         <v>485</v>
       </c>
-      <c r="G23" s="46" t="s">
+      <c r="G23" s="49" t="s">
         <v>486</v>
       </c>
-      <c r="H23" s="46" t="s">
+      <c r="H23" s="49" t="s">
         <v>560</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="35" t="s">
+    <row r="24" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="36" t="s">
         <v>561</v>
       </c>
       <c r="B24" s="10">
         <v>33</v>
       </c>
-      <c r="C24" s="36">
-        <v>0.51515151515151514</v>
+      <c r="C24" s="37">
+        <v>0.5151515151515151</v>
       </c>
       <c r="D24" s="10" t="s">
         <v>562</v>
@@ -33941,15 +33925,15 @@
         <v>566</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="38" t="s">
+    <row r="25" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="39" t="s">
         <v>567</v>
       </c>
       <c r="B25" s="18">
         <v>31</v>
       </c>
-      <c r="C25" s="39">
-        <v>0.64516129032258063</v>
+      <c r="C25" s="40">
+        <v>0.6451612903225806</v>
       </c>
       <c r="D25" s="18" t="s">
         <v>568</v>
@@ -33967,15 +33951,15 @@
         <v>572</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="35" t="s">
+    <row r="26" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="36" t="s">
         <v>573</v>
       </c>
       <c r="B26" s="10">
         <v>29</v>
       </c>
-      <c r="C26" s="36">
-        <v>0.48275862068965519</v>
+      <c r="C26" s="37">
+        <v>0.4827586206896552</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>574</v>
@@ -33993,14 +33977,14 @@
         <v>578</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="38" t="s">
+    <row r="27" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="39" t="s">
         <v>579</v>
       </c>
       <c r="B27" s="18">
         <v>110</v>
       </c>
-      <c r="C27" s="42">
+      <c r="C27" s="43">
         <v>0.45454545454545453</v>
       </c>
       <c r="D27" s="18" t="s">
@@ -34019,65 +34003,65 @@
         <v>584</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="54" t="s">
+    <row r="28" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="50" t="s">
         <v>585</v>
       </c>
-      <c r="B28" s="54"/>
-      <c r="C28" s="54"/>
-      <c r="D28" s="54"/>
-      <c r="E28" s="54"/>
-      <c r="F28" s="54"/>
-      <c r="G28" s="54"/>
-      <c r="H28" s="54"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
+      <c r="D28" s="50"/>
+      <c r="E28" s="50"/>
+      <c r="F28" s="50"/>
+      <c r="G28" s="50"/>
+      <c r="H28" s="50"/>
     </row>
-    <row r="30" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="53" t="s">
+    <row r="30" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="46" t="s">
         <v>586</v>
       </c>
-      <c r="B30" s="53"/>
-      <c r="C30" s="53"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="53"/>
-      <c r="G30" s="53"/>
-      <c r="H30" s="53"/>
+      <c r="B30" s="46"/>
+      <c r="C30" s="46"/>
+      <c r="D30" s="46"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="46"/>
+      <c r="G30" s="46"/>
+      <c r="H30" s="46"/>
     </row>
-    <row r="31" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="46" t="s">
+    <row r="31" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="49" t="s">
         <v>587</v>
       </c>
-      <c r="B31" s="46" t="s">
+      <c r="B31" s="49" t="s">
         <v>479</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="49" t="s">
         <v>559</v>
       </c>
-      <c r="D31" s="46" t="s">
+      <c r="D31" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E31" s="46" t="s">
+      <c r="E31" s="49" t="s">
         <v>588</v>
       </c>
-      <c r="F31" s="46" t="s">
+      <c r="F31" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="G31" s="46" t="s">
+      <c r="G31" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H31" s="46" t="s">
+      <c r="H31" s="49" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="32" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="35" t="s">
+    <row r="32" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="36" t="s">
         <v>590</v>
       </c>
       <c r="B32" s="10">
         <v>9</v>
       </c>
-      <c r="C32" s="41">
-        <v>0.44444444444444442</v>
+      <c r="C32" s="42">
+        <v>0.4444444444444444</v>
       </c>
       <c r="D32" s="10" t="s">
         <v>591</v>
@@ -34095,8 +34079,8 @@
         <v>593</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="38" t="s">
+    <row r="33" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="39" t="s">
         <v>594</v>
       </c>
       <c r="B33" s="18">
@@ -34121,15 +34105,15 @@
         <v>595</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="35" t="s">
+    <row r="34" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="36" t="s">
         <v>596</v>
       </c>
       <c r="B34" s="10">
         <v>27</v>
       </c>
-      <c r="C34" s="39">
-        <v>0.62962962962962965</v>
+      <c r="C34" s="40">
+        <v>0.6296296296296297</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>597</v>
@@ -34147,14 +34131,14 @@
         <v>599</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="38" t="s">
+    <row r="35" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="39" t="s">
         <v>600</v>
       </c>
       <c r="B35" s="18">
         <v>167</v>
       </c>
-      <c r="C35" s="42">
+      <c r="C35" s="43">
         <v>0.47904191616766467</v>
       </c>
       <c r="D35" s="18" t="s">
@@ -34173,53 +34157,53 @@
         <v>603</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="53" t="s">
+    <row r="37" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="46" t="s">
         <v>604</v>
       </c>
-      <c r="B37" s="53"/>
-      <c r="C37" s="53"/>
-      <c r="D37" s="53"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="53"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="46"/>
+      <c r="D37" s="46"/>
+      <c r="E37" s="46"/>
+      <c r="F37" s="46"/>
+      <c r="G37" s="46"/>
+      <c r="H37" s="46"/>
     </row>
-    <row r="38" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="46" t="s">
+    <row r="38" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="49" t="s">
         <v>605</v>
       </c>
-      <c r="B38" s="46" t="s">
+      <c r="B38" s="49" t="s">
         <v>479</v>
       </c>
-      <c r="C38" s="46" t="s">
+      <c r="C38" s="49" t="s">
         <v>559</v>
       </c>
-      <c r="D38" s="46" t="s">
+      <c r="D38" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="46" t="s">
+      <c r="E38" s="49" t="s">
         <v>588</v>
       </c>
-      <c r="F38" s="46" t="s">
+      <c r="F38" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="G38" s="46" t="s">
+      <c r="G38" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="H38" s="46" t="s">
+      <c r="H38" s="49" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="35" t="s">
+    <row r="39" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="36" t="s">
         <v>606</v>
       </c>
       <c r="B39" s="10">
         <v>101</v>
       </c>
-      <c r="C39" s="36">
-        <v>0.50495049504950495</v>
+      <c r="C39" s="37">
+        <v>0.504950495049505</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>554</v>
@@ -34237,14 +34221,14 @@
         <v>608</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="38" t="s">
+    <row r="40" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="39" t="s">
         <v>609</v>
       </c>
       <c r="B40" s="18">
         <v>101</v>
       </c>
-      <c r="C40" s="42">
+      <c r="C40" s="43">
         <v>0.48514851485148514</v>
       </c>
       <c r="D40" s="18" t="s">
@@ -34263,46 +34247,46 @@
         <v>612</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="53" t="s">
+    <row r="42" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="46" t="s">
         <v>613</v>
       </c>
-      <c r="B42" s="53"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="53"/>
-      <c r="E42" s="53"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="53"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="46"/>
+      <c r="F42" s="46"/>
+      <c r="G42" s="46"/>
+      <c r="H42" s="46"/>
     </row>
-    <row r="43" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="46" t="s">
+    <row r="43" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="49" t="s">
         <v>605</v>
       </c>
-      <c r="B43" s="46" t="s">
+      <c r="B43" s="49" t="s">
         <v>24</v>
       </c>
-      <c r="C43" s="46" t="s">
+      <c r="C43" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="D43" s="46" t="s">
+      <c r="D43" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="46" t="s">
+      <c r="E43" s="49" t="s">
         <v>30</v>
       </c>
-      <c r="F43" s="46" t="s">
+      <c r="F43" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="G43" s="46" t="s">
+      <c r="G43" s="49" t="s">
         <v>26</v>
       </c>
-      <c r="H43" s="46" t="s">
+      <c r="H43" s="49" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="35" t="s">
+    <row r="44" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="36" t="s">
         <v>480</v>
       </c>
       <c r="B44" s="10">
@@ -34327,8 +34311,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="38" t="s">
+    <row r="45" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="39" t="s">
         <v>481</v>
       </c>
       <c r="B45" s="18">
@@ -34353,8 +34337,8 @@
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="35" t="s">
+    <row r="46" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="36" t="s">
         <v>614</v>
       </c>
       <c r="B46" s="10">
@@ -34379,8 +34363,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="38" t="s">
+    <row r="47" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="39" t="s">
         <v>615</v>
       </c>
       <c r="B47" s="18">
@@ -34405,49 +34389,49 @@
         <v>13</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="53" t="s">
+    <row r="49" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="46" t="s">
         <v>616</v>
       </c>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="53"/>
+      <c r="B49" s="46"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="46"/>
+      <c r="G49" s="46"/>
+      <c r="H49" s="46"/>
     </row>
-    <row r="50" spans="1:8" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="46" t="s">
+    <row r="50" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="49" t="s">
         <v>617</v>
       </c>
-      <c r="B50" s="46" t="s">
+      <c r="B50" s="49" t="s">
         <v>618</v>
       </c>
-      <c r="C50" s="46" t="s">
+      <c r="C50" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="D50" s="46" t="s">
-        <v>0</v>
-      </c>
-      <c r="E50" s="46" t="s">
+      <c r="D50" s="49" t="s">
+        <v>0</v>
+      </c>
+      <c r="E50" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="F50" s="46" t="s">
+      <c r="F50" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="G50" s="46" t="s">
+      <c r="G50" s="49" t="s">
         <v>608</v>
       </c>
-      <c r="H50" s="46" t="s">
+      <c r="H50" s="49" t="s">
         <v>608</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="44" t="s">
+    <row r="51" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="47" t="s">
         <v>619</v>
       </c>
-      <c r="B51" s="47">
+      <c r="B51" s="51">
         <v>31</v>
       </c>
       <c r="C51" s="10" t="s">
@@ -34469,11 +34453,11 @@
         <v>608</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="45" t="s">
+    <row r="52" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="48" t="s">
         <v>620</v>
       </c>
-      <c r="B52" s="48">
+      <c r="B52" s="52">
         <v>2536</v>
       </c>
       <c r="C52" s="18" t="s">
@@ -34495,11 +34479,11 @@
         <v>608</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="44" t="s">
+    <row r="53" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="47" t="s">
         <v>621</v>
       </c>
-      <c r="B53" s="49">
+      <c r="B53" s="53">
         <v>11.2</v>
       </c>
       <c r="C53" s="10" t="s">
@@ -34521,11 +34505,11 @@
         <v>608</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="45" t="s">
+    <row r="54" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="48" t="s">
         <v>622</v>
       </c>
-      <c r="B54" s="48">
+      <c r="B54" s="52">
         <v>756</v>
       </c>
       <c r="C54" s="18" t="s">
@@ -34547,11 +34531,11 @@
         <v>608</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="44" t="s">
+    <row r="55" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="47" t="s">
         <v>623</v>
       </c>
-      <c r="B55" s="50">
+      <c r="B55" s="54">
         <v>116</v>
       </c>
       <c r="C55" s="10" t="s">
@@ -34575,16 +34559,16 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A37:H37"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A49:H49"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A22:H22"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A49:H49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/Suivi_Comportemental_Challenger.xlsx
+++ b/Suivi_Comportemental_Challenger.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2599" uniqueCount="573">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2690" uniqueCount="583">
   <si>
     <t>Date</t>
   </si>
@@ -1264,6 +1264,36 @@
     <t>42:56</t>
   </si>
   <si>
+    <t>35:22</t>
+  </si>
+  <si>
+    <t>18:14</t>
+  </si>
+  <si>
+    <t>23:21</t>
+  </si>
+  <si>
+    <t>1:11</t>
+  </si>
+  <si>
+    <t>24/03/2026</t>
+  </si>
+  <si>
+    <t>22:23</t>
+  </si>
+  <si>
+    <t>23:01</t>
+  </si>
+  <si>
+    <t>29:06</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>34:22</t>
+  </si>
+  <si>
     <t>Stats par Champion  —  trie par parties jouees</t>
   </si>
   <si>
@@ -1312,6 +1342,9 @@
     <t>Duree Moy.</t>
   </si>
   <si>
+    <t>28:15</t>
+  </si>
+  <si>
     <t>28:57</t>
   </si>
   <si>
@@ -1321,18 +1354,18 @@
     <t>30:34</t>
   </si>
   <si>
-    <t>29:51</t>
-  </si>
-  <si>
-    <t>25:55</t>
+    <t>26:43</t>
+  </si>
+  <si>
+    <t>25:45</t>
+  </si>
+  <si>
+    <t>31:50</t>
   </si>
   <si>
     <t>23:27</t>
   </si>
   <si>
-    <t>32:44</t>
-  </si>
-  <si>
     <t>Comparaison Solo vs Duo</t>
   </si>
   <si>
@@ -1408,19 +1441,19 @@
     <t>KDA moyen</t>
   </si>
   <si>
-    <t>3.40</t>
+    <t>3.38</t>
   </si>
   <si>
     <t>K / D / A moyens</t>
   </si>
   <si>
-    <t>10.8 / 8.0 / 6.8</t>
+    <t>10.7 / 7.9 / 6.8</t>
   </si>
   <si>
     <t>CS/Min moyen</t>
   </si>
   <si>
-    <t>6.8</t>
+    <t>6.7</t>
   </si>
   <si>
     <t>DPM moyen</t>
@@ -1432,19 +1465,19 @@
     <t>% DMG Equipe moyen</t>
   </si>
   <si>
-    <t>27.7 %</t>
+    <t>28.3 %</t>
   </si>
   <si>
     <t>KP % moyen</t>
   </si>
   <si>
-    <t>54.2 %</t>
+    <t>54.0 %</t>
   </si>
   <si>
     <t>Vision Score moyen</t>
   </si>
   <si>
-    <t>23.1</t>
+    <t>22.9</t>
   </si>
   <si>
     <t>Serie Actuelle &amp; Tendance</t>
@@ -1498,73 +1531,73 @@
     <t>Partie 1</t>
   </si>
   <si>
-    <t>3.63</t>
-  </si>
-  <si>
-    <t>12.4</t>
-  </si>
-  <si>
-    <t>7.8</t>
-  </si>
-  <si>
-    <t>6.0</t>
-  </si>
-  <si>
-    <t>6.7 | 1069</t>
+    <t>3.67</t>
+  </si>
+  <si>
+    <t>12.3</t>
+  </si>
+  <si>
+    <t>7.5</t>
+  </si>
+  <si>
+    <t>5.9</t>
+  </si>
+  <si>
+    <t>6.6 | 1105</t>
   </si>
   <si>
     <t>Partie 2</t>
   </si>
   <si>
-    <t>4.07</t>
-  </si>
-  <si>
-    <t>7.2</t>
-  </si>
-  <si>
-    <t>8.4</t>
-  </si>
-  <si>
-    <t>7.7 | 1186</t>
+    <t>3.92</t>
+  </si>
+  <si>
+    <t>12.1</t>
+  </si>
+  <si>
+    <t>7.0</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>7.6 | 1171</t>
   </si>
   <si>
     <t>Partie 3</t>
   </si>
   <si>
-    <t>4.71</t>
-  </si>
-  <si>
-    <t>13.7</t>
-  </si>
-  <si>
-    <t>7.6</t>
-  </si>
-  <si>
-    <t>7.3</t>
-  </si>
-  <si>
-    <t>7.6 | 1314</t>
+    <t>3.87</t>
+  </si>
+  <si>
+    <t>13.4</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>7.5 | 1284</t>
   </si>
   <si>
     <t>Partie 4+</t>
   </si>
   <si>
-    <t>2.80</t>
-  </si>
-  <si>
-    <t>9.2</t>
-  </si>
-  <si>
-    <t>8.3</t>
-  </si>
-  <si>
-    <t>6.4</t>
-  </si>
-  <si>
-    <t>6.3 | 982</t>
-  </si>
-  <si>
-    <t>Diagnostic : ⚠ Fatigue forte (-19.3% WR P1→P4+)</t>
+    <t>3.02</t>
+  </si>
+  <si>
+    <t>9.1</t>
+  </si>
+  <si>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>6.6</t>
+  </si>
+  <si>
+    <t>6.4 | 982</t>
+  </si>
+  <si>
+    <t>Diagnostic : ! Legere fatigue (-14.8% WR P1→P4+)</t>
   </si>
   <si>
     <t>Performance par Tranche Horaire</t>
@@ -1609,10 +1642,10 @@
     <t>Soir (18h-24h)</t>
   </si>
   <si>
-    <t>3.18</t>
-  </si>
-  <si>
-    <t>10.4/8.1/6.5</t>
+    <t>3.17</t>
+  </si>
+  <si>
+    <t>10.2/8.0/6.5</t>
   </si>
   <si>
     <t>Neutre</t>
@@ -1627,10 +1660,10 @@
     <t>Apres une Victoire</t>
   </si>
   <si>
-    <t>4.24</t>
-  </si>
-  <si>
-    <t>11.4/7.2/7.0</t>
+    <t>4.17</t>
+  </si>
+  <si>
+    <t>11.2/7.1/6.9</t>
   </si>
   <si>
     <t/>
@@ -1639,10 +1672,10 @@
     <t>Apres une Defaite</t>
   </si>
   <si>
-    <t>2.54</t>
-  </si>
-  <si>
-    <t>10.3/8.7/6.5</t>
+    <t>2.52</t>
+  </si>
+  <si>
+    <t>10.1/8.7/6.6</t>
   </si>
   <si>
     <t>Tilt detecte — Stopper apres defaite</t>
@@ -1669,10 +1702,10 @@
     <t>0 gank(s) mortel(s)</t>
   </si>
   <si>
-    <t>4.88</t>
-  </si>
-  <si>
-    <t>10.2/6.3/6.2</t>
+    <t>4.75</t>
+  </si>
+  <si>
+    <t>9.8/6.2/6.1</t>
   </si>
   <si>
     <t>Excellente resistance</t>
@@ -1681,10 +1714,7 @@
     <t>1 gank(s) mortel(s)</t>
   </si>
   <si>
-    <t>3.20</t>
-  </si>
-  <si>
-    <t>11.3/8.3/6.7</t>
+    <t>11.3/8.4/6.8</t>
   </si>
   <si>
     <t>Stable</t>
@@ -1693,19 +1723,19 @@
     <t>2 gank(s) mortel(s)</t>
   </si>
   <si>
-    <t>2.64</t>
-  </si>
-  <si>
-    <t>12.6/8.5/7.9</t>
+    <t>2.83</t>
+  </si>
+  <si>
+    <t>12.7/8.3/8.0</t>
   </si>
   <si>
     <t>3+ ganks mortels</t>
   </si>
   <si>
-    <t>1.62</t>
-  </si>
-  <si>
-    <t>8.3/9.8/6.4</t>
+    <t>1.57</t>
+  </si>
+  <si>
+    <t>8.0/9.8/6.3</t>
   </si>
   <si>
     <t>Impact critique</t>
@@ -2484,7 +2514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BB151"/>
+  <dimension ref="A1:BB157"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -2693,7 +2723,7 @@
         <v>55</v>
       </c>
       <c r="C2" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D2" s="10">
         <v>3</v>
@@ -2857,7 +2887,7 @@
         <v>67</v>
       </c>
       <c r="C3" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" s="24">
         <v>2</v>
@@ -3021,7 +3051,7 @@
         <v>72</v>
       </c>
       <c r="C4" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" s="10">
         <v>1</v>
@@ -3185,7 +3215,7 @@
         <v>78</v>
       </c>
       <c r="C5" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="24">
         <v>8</v>
@@ -3349,7 +3379,7 @@
         <v>85</v>
       </c>
       <c r="C6" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D6" s="10">
         <v>7</v>
@@ -3513,7 +3543,7 @@
         <v>90</v>
       </c>
       <c r="C7" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D7" s="24">
         <v>6</v>
@@ -3677,7 +3707,7 @@
         <v>93</v>
       </c>
       <c r="C8" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D8" s="10">
         <v>5</v>
@@ -3841,7 +3871,7 @@
         <v>96</v>
       </c>
       <c r="C9" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D9" s="24">
         <v>4</v>
@@ -4005,7 +4035,7 @@
         <v>100</v>
       </c>
       <c r="C10" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="10">
         <v>3</v>
@@ -4169,7 +4199,7 @@
         <v>103</v>
       </c>
       <c r="C11" s="24">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D11" s="24">
         <v>2</v>
@@ -4333,7 +4363,7 @@
         <v>106</v>
       </c>
       <c r="C12" s="10">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D12" s="10">
         <v>1</v>
@@ -4497,7 +4527,7 @@
         <v>109</v>
       </c>
       <c r="C13" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D13" s="24">
         <v>9</v>
@@ -4661,7 +4691,7 @@
         <v>112</v>
       </c>
       <c r="C14" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D14" s="10">
         <v>8</v>
@@ -4825,7 +4855,7 @@
         <v>55</v>
       </c>
       <c r="C15" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D15" s="24">
         <v>7</v>
@@ -4989,7 +5019,7 @@
         <v>116</v>
       </c>
       <c r="C16" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="10">
         <v>6</v>
@@ -5153,7 +5183,7 @@
         <v>119</v>
       </c>
       <c r="C17" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D17" s="24">
         <v>5</v>
@@ -5317,7 +5347,7 @@
         <v>122</v>
       </c>
       <c r="C18" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D18" s="10">
         <v>4</v>
@@ -5481,7 +5511,7 @@
         <v>124</v>
       </c>
       <c r="C19" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D19" s="24">
         <v>3</v>
@@ -5645,7 +5675,7 @@
         <v>126</v>
       </c>
       <c r="C20" s="10">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D20" s="10">
         <v>2</v>
@@ -5809,7 +5839,7 @@
         <v>128</v>
       </c>
       <c r="C21" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D21" s="24">
         <v>1</v>
@@ -5973,7 +6003,7 @@
         <v>130</v>
       </c>
       <c r="C22" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D22" s="10">
         <v>7</v>
@@ -6137,7 +6167,7 @@
         <v>133</v>
       </c>
       <c r="C23" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D23" s="24">
         <v>6</v>
@@ -6301,7 +6331,7 @@
         <v>135</v>
       </c>
       <c r="C24" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D24" s="10">
         <v>5</v>
@@ -6465,7 +6495,7 @@
         <v>139</v>
       </c>
       <c r="C25" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D25" s="24">
         <v>4</v>
@@ -6629,7 +6659,7 @@
         <v>141</v>
       </c>
       <c r="C26" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D26" s="10">
         <v>3</v>
@@ -6793,7 +6823,7 @@
         <v>144</v>
       </c>
       <c r="C27" s="24">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D27" s="24">
         <v>2</v>
@@ -6957,7 +6987,7 @@
         <v>146</v>
       </c>
       <c r="C28" s="10">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D28" s="10">
         <v>1</v>
@@ -7121,7 +7151,7 @@
         <v>149</v>
       </c>
       <c r="C29" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D29" s="24">
         <v>4</v>
@@ -7285,7 +7315,7 @@
         <v>151</v>
       </c>
       <c r="C30" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D30" s="10">
         <v>3</v>
@@ -7449,7 +7479,7 @@
         <v>154</v>
       </c>
       <c r="C31" s="24">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D31" s="24">
         <v>2</v>
@@ -7613,7 +7643,7 @@
         <v>156</v>
       </c>
       <c r="C32" s="10">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D32" s="10">
         <v>1</v>
@@ -7777,7 +7807,7 @@
         <v>158</v>
       </c>
       <c r="C33" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D33" s="24">
         <v>9</v>
@@ -7941,7 +7971,7 @@
         <v>160</v>
       </c>
       <c r="C34" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D34" s="10">
         <v>8</v>
@@ -8105,7 +8135,7 @@
         <v>164</v>
       </c>
       <c r="C35" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D35" s="24">
         <v>7</v>
@@ -8269,7 +8299,7 @@
         <v>167</v>
       </c>
       <c r="C36" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D36" s="10">
         <v>6</v>
@@ -8433,7 +8463,7 @@
         <v>170</v>
       </c>
       <c r="C37" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D37" s="24">
         <v>5</v>
@@ -8597,7 +8627,7 @@
         <v>85</v>
       </c>
       <c r="C38" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D38" s="10">
         <v>4</v>
@@ -8761,7 +8791,7 @@
         <v>174</v>
       </c>
       <c r="C39" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D39" s="24">
         <v>3</v>
@@ -8925,7 +8955,7 @@
         <v>176</v>
       </c>
       <c r="C40" s="10">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D40" s="10">
         <v>2</v>
@@ -9089,7 +9119,7 @@
         <v>178</v>
       </c>
       <c r="C41" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41" s="24">
         <v>1</v>
@@ -9253,7 +9283,7 @@
         <v>180</v>
       </c>
       <c r="C42" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D42" s="10">
         <v>9</v>
@@ -9417,7 +9447,7 @@
         <v>183</v>
       </c>
       <c r="C43" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D43" s="24">
         <v>8</v>
@@ -9581,7 +9611,7 @@
         <v>186</v>
       </c>
       <c r="C44" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D44" s="10">
         <v>7</v>
@@ -9745,7 +9775,7 @@
         <v>189</v>
       </c>
       <c r="C45" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D45" s="24">
         <v>6</v>
@@ -9909,7 +9939,7 @@
         <v>192</v>
       </c>
       <c r="C46" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D46" s="10">
         <v>5</v>
@@ -10073,7 +10103,7 @@
         <v>194</v>
       </c>
       <c r="C47" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D47" s="24">
         <v>4</v>
@@ -10237,7 +10267,7 @@
         <v>197</v>
       </c>
       <c r="C48" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D48" s="10">
         <v>3</v>
@@ -10401,7 +10431,7 @@
         <v>200</v>
       </c>
       <c r="C49" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D49" s="24">
         <v>2</v>
@@ -10565,7 +10595,7 @@
         <v>203</v>
       </c>
       <c r="C50" s="10">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D50" s="10">
         <v>1</v>
@@ -10729,7 +10759,7 @@
         <v>206</v>
       </c>
       <c r="C51" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D51" s="24">
         <v>1</v>
@@ -10893,7 +10923,7 @@
         <v>209</v>
       </c>
       <c r="C52" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D52" s="10">
         <v>6</v>
@@ -11057,7 +11087,7 @@
         <v>212</v>
       </c>
       <c r="C53" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D53" s="24">
         <v>5</v>
@@ -11221,7 +11251,7 @@
         <v>214</v>
       </c>
       <c r="C54" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D54" s="10">
         <v>4</v>
@@ -11385,7 +11415,7 @@
         <v>217</v>
       </c>
       <c r="C55" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D55" s="24">
         <v>3</v>
@@ -11549,7 +11579,7 @@
         <v>219</v>
       </c>
       <c r="C56" s="10">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D56" s="10">
         <v>2</v>
@@ -11713,7 +11743,7 @@
         <v>221</v>
       </c>
       <c r="C57" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D57" s="24">
         <v>1</v>
@@ -11877,7 +11907,7 @@
         <v>225</v>
       </c>
       <c r="C58" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D58" s="10">
         <v>6</v>
@@ -12041,7 +12071,7 @@
         <v>112</v>
       </c>
       <c r="C59" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D59" s="24">
         <v>5</v>
@@ -12205,7 +12235,7 @@
         <v>227</v>
       </c>
       <c r="C60" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D60" s="10">
         <v>4</v>
@@ -12369,7 +12399,7 @@
         <v>229</v>
       </c>
       <c r="C61" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D61" s="24">
         <v>3</v>
@@ -12533,7 +12563,7 @@
         <v>231</v>
       </c>
       <c r="C62" s="10">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D62" s="10">
         <v>2</v>
@@ -12697,7 +12727,7 @@
         <v>233</v>
       </c>
       <c r="C63" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D63" s="24">
         <v>1</v>
@@ -12861,7 +12891,7 @@
         <v>112</v>
       </c>
       <c r="C64" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D64" s="10">
         <v>6</v>
@@ -13025,7 +13055,7 @@
         <v>194</v>
       </c>
       <c r="C65" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D65" s="24">
         <v>5</v>
@@ -13189,7 +13219,7 @@
         <v>240</v>
       </c>
       <c r="C66" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D66" s="10">
         <v>4</v>
@@ -13353,7 +13383,7 @@
         <v>242</v>
       </c>
       <c r="C67" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D67" s="24">
         <v>3</v>
@@ -13517,7 +13547,7 @@
         <v>244</v>
       </c>
       <c r="C68" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D68" s="10">
         <v>2</v>
@@ -13681,7 +13711,7 @@
         <v>246</v>
       </c>
       <c r="C69" s="24">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D69" s="24">
         <v>1</v>
@@ -13845,7 +13875,7 @@
         <v>250</v>
       </c>
       <c r="C70" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D70" s="10">
         <v>9</v>
@@ -14009,7 +14039,7 @@
         <v>253</v>
       </c>
       <c r="C71" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D71" s="24">
         <v>8</v>
@@ -14173,7 +14203,7 @@
         <v>255</v>
       </c>
       <c r="C72" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D72" s="10">
         <v>7</v>
@@ -14337,7 +14367,7 @@
         <v>257</v>
       </c>
       <c r="C73" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D73" s="24">
         <v>6</v>
@@ -14501,7 +14531,7 @@
         <v>260</v>
       </c>
       <c r="C74" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D74" s="10">
         <v>5</v>
@@ -14665,7 +14695,7 @@
         <v>116</v>
       </c>
       <c r="C75" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D75" s="24">
         <v>4</v>
@@ -14829,7 +14859,7 @@
         <v>263</v>
       </c>
       <c r="C76" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D76" s="10">
         <v>3</v>
@@ -14993,7 +15023,7 @@
         <v>144</v>
       </c>
       <c r="C77" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D77" s="24">
         <v>2</v>
@@ -15157,7 +15187,7 @@
         <v>219</v>
       </c>
       <c r="C78" s="10">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D78" s="10">
         <v>1</v>
@@ -15321,7 +15351,7 @@
         <v>267</v>
       </c>
       <c r="C79" s="24">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D79" s="24">
         <v>1</v>
@@ -15485,7 +15515,7 @@
         <v>269</v>
       </c>
       <c r="C80" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D80" s="10">
         <v>9</v>
@@ -15649,7 +15679,7 @@
         <v>271</v>
       </c>
       <c r="C81" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D81" s="24">
         <v>8</v>
@@ -15813,7 +15843,7 @@
         <v>274</v>
       </c>
       <c r="C82" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D82" s="10">
         <v>7</v>
@@ -15977,7 +16007,7 @@
         <v>276</v>
       </c>
       <c r="C83" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D83" s="24">
         <v>6</v>
@@ -16141,7 +16171,7 @@
         <v>170</v>
       </c>
       <c r="C84" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D84" s="10">
         <v>5</v>
@@ -16305,7 +16335,7 @@
         <v>280</v>
       </c>
       <c r="C85" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D85" s="24">
         <v>4</v>
@@ -16469,7 +16499,7 @@
         <v>282</v>
       </c>
       <c r="C86" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D86" s="10">
         <v>3</v>
@@ -16633,7 +16663,7 @@
         <v>157</v>
       </c>
       <c r="C87" s="24">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D87" s="24">
         <v>2</v>
@@ -16797,7 +16827,7 @@
         <v>285</v>
       </c>
       <c r="C88" s="10">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D88" s="10">
         <v>1</v>
@@ -16961,7 +16991,7 @@
         <v>288</v>
       </c>
       <c r="C89" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D89" s="24">
         <v>9</v>
@@ -17125,7 +17155,7 @@
         <v>290</v>
       </c>
       <c r="C90" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D90" s="10">
         <v>8</v>
@@ -17289,7 +17319,7 @@
         <v>292</v>
       </c>
       <c r="C91" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D91" s="24">
         <v>7</v>
@@ -17453,7 +17483,7 @@
         <v>294</v>
       </c>
       <c r="C92" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D92" s="10">
         <v>6</v>
@@ -17617,7 +17647,7 @@
         <v>93</v>
       </c>
       <c r="C93" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D93" s="24">
         <v>5</v>
@@ -17781,7 +17811,7 @@
         <v>298</v>
       </c>
       <c r="C94" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D94" s="10">
         <v>4</v>
@@ -17945,7 +17975,7 @@
         <v>300</v>
       </c>
       <c r="C95" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D95" s="24">
         <v>3</v>
@@ -18109,7 +18139,7 @@
         <v>302</v>
       </c>
       <c r="C96" s="10">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D96" s="10">
         <v>2</v>
@@ -18273,7 +18303,7 @@
         <v>304</v>
       </c>
       <c r="C97" s="24">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D97" s="24">
         <v>1</v>
@@ -18437,7 +18467,7 @@
         <v>307</v>
       </c>
       <c r="C98" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D98" s="10">
         <v>7</v>
@@ -18601,7 +18631,7 @@
         <v>294</v>
       </c>
       <c r="C99" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D99" s="24">
         <v>6</v>
@@ -18765,7 +18795,7 @@
         <v>310</v>
       </c>
       <c r="C100" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D100" s="10">
         <v>5</v>
@@ -18929,7 +18959,7 @@
         <v>312</v>
       </c>
       <c r="C101" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D101" s="24">
         <v>4</v>
@@ -19093,7 +19123,7 @@
         <v>314</v>
       </c>
       <c r="C102" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D102" s="10">
         <v>3</v>
@@ -19257,7 +19287,7 @@
         <v>317</v>
       </c>
       <c r="C103" s="24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D103" s="24">
         <v>2</v>
@@ -19421,7 +19451,7 @@
         <v>319</v>
       </c>
       <c r="C104" s="10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D104" s="10">
         <v>1</v>
@@ -19585,7 +19615,7 @@
         <v>321</v>
       </c>
       <c r="C105" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D105" s="24">
         <v>8</v>
@@ -19749,7 +19779,7 @@
         <v>322</v>
       </c>
       <c r="C106" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D106" s="10">
         <v>7</v>
@@ -19913,7 +19943,7 @@
         <v>112</v>
       </c>
       <c r="C107" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D107" s="24">
         <v>6</v>
@@ -20077,7 +20107,7 @@
         <v>325</v>
       </c>
       <c r="C108" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D108" s="10">
         <v>5</v>
@@ -20241,7 +20271,7 @@
         <v>328</v>
       </c>
       <c r="C109" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D109" s="24">
         <v>4</v>
@@ -20405,7 +20435,7 @@
         <v>330</v>
       </c>
       <c r="C110" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D110" s="10">
         <v>3</v>
@@ -20569,7 +20599,7 @@
         <v>314</v>
       </c>
       <c r="C111" s="24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D111" s="24">
         <v>2</v>
@@ -20733,7 +20763,7 @@
         <v>334</v>
       </c>
       <c r="C112" s="10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D112" s="10">
         <v>1</v>
@@ -20897,7 +20927,7 @@
         <v>337</v>
       </c>
       <c r="C113" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D113" s="24">
         <v>5</v>
@@ -21061,7 +21091,7 @@
         <v>339</v>
       </c>
       <c r="C114" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D114" s="10">
         <v>4</v>
@@ -21225,7 +21255,7 @@
         <v>340</v>
       </c>
       <c r="C115" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D115" s="24">
         <v>3</v>
@@ -21389,7 +21419,7 @@
         <v>342</v>
       </c>
       <c r="C116" s="10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D116" s="10">
         <v>2</v>
@@ -21553,7 +21583,7 @@
         <v>344</v>
       </c>
       <c r="C117" s="24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D117" s="24">
         <v>1</v>
@@ -21717,7 +21747,7 @@
         <v>78</v>
       </c>
       <c r="C118" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D118" s="10">
         <v>6</v>
@@ -21881,7 +21911,7 @@
         <v>348</v>
       </c>
       <c r="C119" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D119" s="24">
         <v>5</v>
@@ -22045,7 +22075,7 @@
         <v>350</v>
       </c>
       <c r="C120" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D120" s="10">
         <v>4</v>
@@ -22209,7 +22239,7 @@
         <v>352</v>
       </c>
       <c r="C121" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D121" s="24">
         <v>3</v>
@@ -22373,7 +22403,7 @@
         <v>355</v>
       </c>
       <c r="C122" s="10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D122" s="10">
         <v>2</v>
@@ -22537,7 +22567,7 @@
         <v>357</v>
       </c>
       <c r="C123" s="24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D123" s="24">
         <v>1</v>
@@ -22701,7 +22731,7 @@
         <v>360</v>
       </c>
       <c r="C124" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D124" s="10">
         <v>6</v>
@@ -22865,7 +22895,7 @@
         <v>363</v>
       </c>
       <c r="C125" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D125" s="24">
         <v>5</v>
@@ -23029,7 +23059,7 @@
         <v>365</v>
       </c>
       <c r="C126" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D126" s="10">
         <v>4</v>
@@ -23193,7 +23223,7 @@
         <v>367</v>
       </c>
       <c r="C127" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D127" s="24">
         <v>3</v>
@@ -23357,7 +23387,7 @@
         <v>369</v>
       </c>
       <c r="C128" s="10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D128" s="10">
         <v>2</v>
@@ -23521,7 +23551,7 @@
         <v>371</v>
       </c>
       <c r="C129" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D129" s="24">
         <v>1</v>
@@ -23685,7 +23715,7 @@
         <v>373</v>
       </c>
       <c r="C130" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D130" s="10">
         <v>3</v>
@@ -23849,7 +23879,7 @@
         <v>375</v>
       </c>
       <c r="C131" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D131" s="24">
         <v>2</v>
@@ -24013,7 +24043,7 @@
         <v>377</v>
       </c>
       <c r="C132" s="10">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D132" s="10">
         <v>1</v>
@@ -24177,7 +24207,7 @@
         <v>380</v>
       </c>
       <c r="C133" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D133" s="24">
         <v>11</v>
@@ -24341,7 +24371,7 @@
         <v>382</v>
       </c>
       <c r="C134" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D134" s="10">
         <v>10</v>
@@ -24505,7 +24535,7 @@
         <v>384</v>
       </c>
       <c r="C135" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D135" s="24">
         <v>9</v>
@@ -24669,7 +24699,7 @@
         <v>386</v>
       </c>
       <c r="C136" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D136" s="10">
         <v>8</v>
@@ -24833,7 +24863,7 @@
         <v>389</v>
       </c>
       <c r="C137" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D137" s="24">
         <v>7</v>
@@ -24997,7 +25027,7 @@
         <v>391</v>
       </c>
       <c r="C138" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D138" s="10">
         <v>6</v>
@@ -25161,7 +25191,7 @@
         <v>394</v>
       </c>
       <c r="C139" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D139" s="24">
         <v>5</v>
@@ -25325,7 +25355,7 @@
         <v>272</v>
       </c>
       <c r="C140" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D140" s="10">
         <v>4</v>
@@ -25489,7 +25519,7 @@
         <v>397</v>
       </c>
       <c r="C141" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D141" s="24">
         <v>3</v>
@@ -25653,7 +25683,7 @@
         <v>398</v>
       </c>
       <c r="C142" s="10">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D142" s="10">
         <v>2</v>
@@ -25817,7 +25847,7 @@
         <v>399</v>
       </c>
       <c r="C143" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D143" s="24">
         <v>1</v>
@@ -25981,7 +26011,7 @@
         <v>402</v>
       </c>
       <c r="C144" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D144" s="10">
         <v>5</v>
@@ -26145,7 +26175,7 @@
         <v>363</v>
       </c>
       <c r="C145" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D145" s="24">
         <v>4</v>
@@ -26309,7 +26339,7 @@
         <v>404</v>
       </c>
       <c r="C146" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D146" s="10">
         <v>3</v>
@@ -26473,7 +26503,7 @@
         <v>406</v>
       </c>
       <c r="C147" s="24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D147" s="24">
         <v>2</v>
@@ -26637,7 +26667,7 @@
         <v>408</v>
       </c>
       <c r="C148" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D148" s="10">
         <v>1</v>
@@ -26801,10 +26831,10 @@
         <v>412</v>
       </c>
       <c r="C149" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D149" s="24">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E149" s="24" t="s">
         <v>413</v>
@@ -26965,10 +26995,10 @@
         <v>414</v>
       </c>
       <c r="C150" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D150" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E150" s="10" t="s">
         <v>415</v>
@@ -27129,10 +27159,10 @@
         <v>96</v>
       </c>
       <c r="C151" s="24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D151" s="24">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E151" s="24" t="s">
         <v>408</v>
@@ -27283,6 +27313,990 @@
       </c>
       <c r="BB151" s="24" t="s">
         <v>111</v>
+      </c>
+    </row>
+    <row r="152" ht="20" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A152" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C152" s="10">
+        <v>2</v>
+      </c>
+      <c r="D152" s="10">
+        <v>3</v>
+      </c>
+      <c r="E152" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="F152" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="G152" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="H152" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I152" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="J152" s="12">
+        <v>1.92</v>
+      </c>
+      <c r="K152" s="10">
+        <v>11</v>
+      </c>
+      <c r="L152" s="13">
+        <v>12</v>
+      </c>
+      <c r="M152" s="10">
+        <v>12</v>
+      </c>
+      <c r="N152" s="36">
+        <v>20.2</v>
+      </c>
+      <c r="O152" s="14">
+        <v>50</v>
+      </c>
+      <c r="P152" s="14">
+        <v>21.9</v>
+      </c>
+      <c r="Q152" s="15">
+        <v>2.159</v>
+      </c>
+      <c r="R152" s="41">
+        <v>0.66</v>
+      </c>
+      <c r="S152" s="28">
+        <v>6.1</v>
+      </c>
+      <c r="T152" s="17">
+        <v>430</v>
+      </c>
+      <c r="U152" s="17">
+        <v>928</v>
+      </c>
+      <c r="V152" s="10">
+        <v>962</v>
+      </c>
+      <c r="W152" s="10">
+        <v>30</v>
+      </c>
+      <c r="X152" s="10">
+        <v>2</v>
+      </c>
+      <c r="Y152" s="10">
+        <v>8</v>
+      </c>
+      <c r="Z152" s="10">
+        <v>1</v>
+      </c>
+      <c r="AA152" s="10">
+        <v>39</v>
+      </c>
+      <c r="AB152" s="10">
+        <v>7</v>
+      </c>
+      <c r="AC152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE152" s="10">
+        <v>5</v>
+      </c>
+      <c r="AF152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG152" s="10">
+        <v>1</v>
+      </c>
+      <c r="AH152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ152" s="10">
+        <v>27</v>
+      </c>
+      <c r="AK152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL152" s="10">
+        <v>6</v>
+      </c>
+      <c r="AM152" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN152" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO152" s="18">
+        <v>3</v>
+      </c>
+      <c r="AP152" s="47">
+        <v>40</v>
+      </c>
+      <c r="AQ152" s="19">
+        <v>-4</v>
+      </c>
+      <c r="AR152" s="19">
+        <v>-1071</v>
+      </c>
+      <c r="AS152" s="10">
+        <v>4</v>
+      </c>
+      <c r="AT152" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AU152" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AV152" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AW152" s="21">
+        <v>-0.2</v>
+      </c>
+      <c r="AX152" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY152" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ152" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="BA152" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="BB152" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="153" ht="20" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A153" s="23" t="s">
+        <v>411</v>
+      </c>
+      <c r="B153" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="C153" s="24">
+        <v>2</v>
+      </c>
+      <c r="D153" s="24">
+        <v>2</v>
+      </c>
+      <c r="E153" s="24" t="s">
+        <v>418</v>
+      </c>
+      <c r="F153" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="G153" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="H153" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="I153" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J153" s="35">
+        <v>0.63</v>
+      </c>
+      <c r="K153" s="24">
+        <v>2</v>
+      </c>
+      <c r="L153" s="13">
+        <v>8</v>
+      </c>
+      <c r="M153" s="24">
+        <v>3</v>
+      </c>
+      <c r="N153" s="27">
+        <v>14.6</v>
+      </c>
+      <c r="O153" s="27">
+        <v>50</v>
+      </c>
+      <c r="P153" s="27">
+        <v>26.6</v>
+      </c>
+      <c r="Q153" s="15">
+        <v>1.907</v>
+      </c>
+      <c r="R153" s="41">
+        <v>0.62</v>
+      </c>
+      <c r="S153" s="28">
+        <v>5.8</v>
+      </c>
+      <c r="T153" s="29">
+        <v>345</v>
+      </c>
+      <c r="U153" s="29">
+        <v>659</v>
+      </c>
+      <c r="V153" s="24">
+        <v>389</v>
+      </c>
+      <c r="W153" s="24">
+        <v>12</v>
+      </c>
+      <c r="X153" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y153" s="24">
+        <v>5</v>
+      </c>
+      <c r="Z153" s="24">
+        <v>0</v>
+      </c>
+      <c r="AA153" s="24">
+        <v>27</v>
+      </c>
+      <c r="AB153" s="24">
+        <v>4</v>
+      </c>
+      <c r="AC153" s="24">
+        <v>0</v>
+      </c>
+      <c r="AD153" s="24">
+        <v>0</v>
+      </c>
+      <c r="AE153" s="24">
+        <v>0</v>
+      </c>
+      <c r="AF153" s="24">
+        <v>0</v>
+      </c>
+      <c r="AG153" s="24">
+        <v>3</v>
+      </c>
+      <c r="AH153" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI153" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ153" s="24">
+        <v>23</v>
+      </c>
+      <c r="AK153" s="24">
+        <v>0</v>
+      </c>
+      <c r="AL153" s="24">
+        <v>1</v>
+      </c>
+      <c r="AM153" s="24">
+        <v>0</v>
+      </c>
+      <c r="AN153" s="24">
+        <v>3</v>
+      </c>
+      <c r="AO153" s="19">
+        <v>-5</v>
+      </c>
+      <c r="AP153" s="19">
+        <v>-1115</v>
+      </c>
+      <c r="AQ153" s="19">
+        <v>-45</v>
+      </c>
+      <c r="AR153" s="19">
+        <v>-2560</v>
+      </c>
+      <c r="AS153" s="24">
+        <v>5</v>
+      </c>
+      <c r="AT153" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AU153" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV153" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AW153" s="43">
+        <v>-0.95</v>
+      </c>
+      <c r="AX153" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY153" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ153" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="BA153" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="BB153" s="24" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="154" ht="20" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A154" s="9" t="s">
+        <v>411</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="C154" s="10">
+        <v>2</v>
+      </c>
+      <c r="D154" s="10">
+        <v>1</v>
+      </c>
+      <c r="E154" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="F154" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="G154" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H154" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="I154" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J154" s="35">
+        <v>0</v>
+      </c>
+      <c r="K154" s="10">
+        <v>0</v>
+      </c>
+      <c r="L154" s="33">
+        <v>0</v>
+      </c>
+      <c r="M154" s="10">
+        <v>0</v>
+      </c>
+      <c r="N154" s="14">
+        <v>0</v>
+      </c>
+      <c r="O154" s="14">
+        <v>0</v>
+      </c>
+      <c r="P154" s="14">
+        <v>100</v>
+      </c>
+      <c r="Q154" s="49">
+        <v>0.58</v>
+      </c>
+      <c r="R154" s="41">
+        <v>0.58</v>
+      </c>
+      <c r="S154" s="28">
+        <v>0</v>
+      </c>
+      <c r="T154" s="17">
+        <v>434</v>
+      </c>
+      <c r="U154" s="17">
+        <v>252</v>
+      </c>
+      <c r="V154" s="10">
+        <v>0</v>
+      </c>
+      <c r="W154" s="10">
+        <v>0</v>
+      </c>
+      <c r="X154" s="10">
+        <v>0</v>
+      </c>
+      <c r="Y154" s="10">
+        <v>0</v>
+      </c>
+      <c r="Z154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AB154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AC154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AH154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AK154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AM154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN154" s="10">
+        <v>0</v>
+      </c>
+      <c r="AO154" s="47">
+        <v>0</v>
+      </c>
+      <c r="AP154" s="47">
+        <v>-15</v>
+      </c>
+      <c r="AQ154" s="47">
+        <v>0</v>
+      </c>
+      <c r="AR154" s="47">
+        <v>-15</v>
+      </c>
+      <c r="AS154" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AT154" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AU154" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV154" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AW154" s="21">
+        <v>-0.8</v>
+      </c>
+      <c r="AX154" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY154" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ154" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="BA154" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="BB154" s="10" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="155" ht="20" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A155" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="B155" s="24" t="s">
+        <v>421</v>
+      </c>
+      <c r="C155" s="24">
+        <v>1</v>
+      </c>
+      <c r="D155" s="24">
+        <v>3</v>
+      </c>
+      <c r="E155" s="24" t="s">
+        <v>422</v>
+      </c>
+      <c r="F155" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="G155" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H155" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="I155" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="J155" s="45">
+        <v>3.5</v>
+      </c>
+      <c r="K155" s="24">
+        <v>5</v>
+      </c>
+      <c r="L155" s="24">
+        <v>4</v>
+      </c>
+      <c r="M155" s="24">
+        <v>9</v>
+      </c>
+      <c r="N155" s="27">
+        <v>6.4</v>
+      </c>
+      <c r="O155" s="27">
+        <v>50</v>
+      </c>
+      <c r="P155" s="27">
+        <v>27.6</v>
+      </c>
+      <c r="Q155" s="15">
+        <v>1.689</v>
+      </c>
+      <c r="R155" s="26">
+        <v>1.12</v>
+      </c>
+      <c r="S155" s="27">
+        <v>8.3</v>
+      </c>
+      <c r="T155" s="29">
+        <v>506</v>
+      </c>
+      <c r="U155" s="29">
+        <v>855</v>
+      </c>
+      <c r="V155" s="24">
+        <v>553</v>
+      </c>
+      <c r="W155" s="24">
+        <v>17</v>
+      </c>
+      <c r="X155" s="24">
+        <v>5</v>
+      </c>
+      <c r="Y155" s="24">
+        <v>2</v>
+      </c>
+      <c r="Z155" s="24">
+        <v>0</v>
+      </c>
+      <c r="AA155" s="24">
+        <v>14</v>
+      </c>
+      <c r="AB155" s="24">
+        <v>7</v>
+      </c>
+      <c r="AC155" s="24">
+        <v>0</v>
+      </c>
+      <c r="AD155" s="24">
+        <v>0</v>
+      </c>
+      <c r="AE155" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF155" s="24">
+        <v>0</v>
+      </c>
+      <c r="AG155" s="24">
+        <v>3</v>
+      </c>
+      <c r="AH155" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI155" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ155" s="24">
+        <v>6</v>
+      </c>
+      <c r="AK155" s="24">
+        <v>0</v>
+      </c>
+      <c r="AL155" s="24">
+        <v>4</v>
+      </c>
+      <c r="AM155" s="24">
+        <v>0</v>
+      </c>
+      <c r="AN155" s="24">
+        <v>0</v>
+      </c>
+      <c r="AO155" s="18">
+        <v>8</v>
+      </c>
+      <c r="AP155" s="18">
+        <v>233</v>
+      </c>
+      <c r="AQ155" s="18">
+        <v>11</v>
+      </c>
+      <c r="AR155" s="18">
+        <v>1179</v>
+      </c>
+      <c r="AS155" s="24">
+        <v>3</v>
+      </c>
+      <c r="AT155" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AU155" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="AV155" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AW155" s="43">
+        <v>0.5</v>
+      </c>
+      <c r="AX155" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="AY155" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ155" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="BA155" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="BB155" s="24" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="156" ht="20" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A156" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="B156" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="C156" s="10">
+        <v>1</v>
+      </c>
+      <c r="D156" s="10">
+        <v>2</v>
+      </c>
+      <c r="E156" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="F156" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="G156" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H156" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="I156" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="J156" s="45">
+        <v>3</v>
+      </c>
+      <c r="K156" s="10">
+        <v>13</v>
+      </c>
+      <c r="L156" s="13">
+        <v>6</v>
+      </c>
+      <c r="M156" s="10">
+        <v>5</v>
+      </c>
+      <c r="N156" s="14">
+        <v>8</v>
+      </c>
+      <c r="O156" s="14">
+        <v>75</v>
+      </c>
+      <c r="P156" s="14">
+        <v>36.9</v>
+      </c>
+      <c r="Q156" s="15">
+        <v>2.453</v>
+      </c>
+      <c r="R156" s="16">
+        <v>1.69</v>
+      </c>
+      <c r="S156" s="14">
+        <v>7.7</v>
+      </c>
+      <c r="T156" s="17">
+        <v>540</v>
+      </c>
+      <c r="U156" s="17">
+        <v>1325</v>
+      </c>
+      <c r="V156" s="10">
+        <v>431</v>
+      </c>
+      <c r="W156" s="10">
+        <v>13</v>
+      </c>
+      <c r="X156" s="10">
+        <v>6</v>
+      </c>
+      <c r="Y156" s="10">
+        <v>2</v>
+      </c>
+      <c r="Z156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AA156" s="10">
+        <v>18</v>
+      </c>
+      <c r="AB156" s="10">
+        <v>6</v>
+      </c>
+      <c r="AC156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AD156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AE156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AF156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AG156" s="10">
+        <v>4</v>
+      </c>
+      <c r="AH156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AI156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AJ156" s="10">
+        <v>12</v>
+      </c>
+      <c r="AK156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AL156" s="10">
+        <v>2</v>
+      </c>
+      <c r="AM156" s="10">
+        <v>0</v>
+      </c>
+      <c r="AN156" s="10">
+        <v>1</v>
+      </c>
+      <c r="AO156" s="18">
+        <v>4</v>
+      </c>
+      <c r="AP156" s="18">
+        <v>778</v>
+      </c>
+      <c r="AQ156" s="19">
+        <v>-1</v>
+      </c>
+      <c r="AR156" s="18">
+        <v>1457</v>
+      </c>
+      <c r="AS156" s="10">
+        <v>3</v>
+      </c>
+      <c r="AT156" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AU156" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV156" s="37" t="s">
+        <v>82</v>
+      </c>
+      <c r="AW156" s="31">
+        <v>1.65</v>
+      </c>
+      <c r="AX156" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="AY156" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ156" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="BA156" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="BB156" s="10" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="157" ht="20" customHeight="1" spans="1:54" x14ac:dyDescent="0.25">
+      <c r="A157" s="23" t="s">
+        <v>420</v>
+      </c>
+      <c r="B157" s="24" t="s">
+        <v>424</v>
+      </c>
+      <c r="C157" s="24">
+        <v>1</v>
+      </c>
+      <c r="D157" s="24">
+        <v>1</v>
+      </c>
+      <c r="E157" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="F157" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="G157" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="H157" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="I157" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="J157" s="16">
+        <v>8.67</v>
+      </c>
+      <c r="K157" s="24">
+        <v>15</v>
+      </c>
+      <c r="L157" s="24">
+        <v>3</v>
+      </c>
+      <c r="M157" s="24">
+        <v>11</v>
+      </c>
+      <c r="N157" s="27">
+        <v>4.3</v>
+      </c>
+      <c r="O157" s="27">
+        <v>61.9</v>
+      </c>
+      <c r="P157" s="27">
+        <v>41.1</v>
+      </c>
+      <c r="Q157" s="15">
+        <v>3.534</v>
+      </c>
+      <c r="R157" s="16">
+        <v>3.07</v>
+      </c>
+      <c r="S157" s="46">
+        <v>9.7</v>
+      </c>
+      <c r="T157" s="29">
+        <v>652</v>
+      </c>
+      <c r="U157" s="29">
+        <v>2303</v>
+      </c>
+      <c r="V157" s="24">
+        <v>988</v>
+      </c>
+      <c r="W157" s="24">
+        <v>27</v>
+      </c>
+      <c r="X157" s="24">
+        <v>10</v>
+      </c>
+      <c r="Y157" s="24">
+        <v>6</v>
+      </c>
+      <c r="Z157" s="24">
+        <v>0</v>
+      </c>
+      <c r="AA157" s="24">
+        <v>25</v>
+      </c>
+      <c r="AB157" s="24">
+        <v>2</v>
+      </c>
+      <c r="AC157" s="24">
+        <v>0</v>
+      </c>
+      <c r="AD157" s="24">
+        <v>0</v>
+      </c>
+      <c r="AE157" s="24">
+        <v>0</v>
+      </c>
+      <c r="AF157" s="24">
+        <v>0</v>
+      </c>
+      <c r="AG157" s="24">
+        <v>1</v>
+      </c>
+      <c r="AH157" s="24">
+        <v>0</v>
+      </c>
+      <c r="AI157" s="24">
+        <v>0</v>
+      </c>
+      <c r="AJ157" s="24">
+        <v>22</v>
+      </c>
+      <c r="AK157" s="24">
+        <v>1</v>
+      </c>
+      <c r="AL157" s="24">
+        <v>1</v>
+      </c>
+      <c r="AM157" s="24">
+        <v>0</v>
+      </c>
+      <c r="AN157" s="24">
+        <v>2</v>
+      </c>
+      <c r="AO157" s="18">
+        <v>20</v>
+      </c>
+      <c r="AP157" s="18">
+        <v>868</v>
+      </c>
+      <c r="AQ157" s="18">
+        <v>24</v>
+      </c>
+      <c r="AR157" s="18">
+        <v>1615</v>
+      </c>
+      <c r="AS157" s="24">
+        <v>4</v>
+      </c>
+      <c r="AT157" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AU157" s="37" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV157" s="37" t="s">
+        <v>173</v>
+      </c>
+      <c r="AW157" s="31">
+        <v>1.75</v>
+      </c>
+      <c r="AX157" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="AY157" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="AZ157" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="BA157" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="BB157" s="24" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -27311,7 +28325,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" s="50" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="B1" s="50"/>
       <c r="C1" s="50"/>
@@ -27336,46 +28350,46 @@
         <v>5</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C2" s="51" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="D2" s="51" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="E2" s="51" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="F2" s="51" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="G2" s="51" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="H2" s="51" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="I2" s="51" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="J2" s="51" t="s">
-        <v>425</v>
+        <v>435</v>
       </c>
       <c r="K2" s="51" t="s">
-        <v>426</v>
+        <v>436</v>
       </c>
       <c r="L2" s="51" t="s">
-        <v>427</v>
+        <v>437</v>
       </c>
       <c r="M2" s="51" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="N2" s="51" t="s">
-        <v>429</v>
+        <v>439</v>
       </c>
       <c r="O2" s="51" t="s">
-        <v>430</v>
+        <v>440</v>
       </c>
       <c r="P2" s="51" t="s">
         <v>81</v>
@@ -27384,7 +28398,7 @@
         <v>59</v>
       </c>
       <c r="R2" s="51" t="s">
-        <v>431</v>
+        <v>441</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -27392,22 +28406,22 @@
         <v>87</v>
       </c>
       <c r="B3" s="10">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C3" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="10">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="53">
-        <v>0.48484848484848486</v>
+        <v>0.4852941176470588</v>
       </c>
       <c r="F3" s="12">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G3" s="10">
-        <v>9.9</v>
+        <v>9.8</v>
       </c>
       <c r="H3" s="13">
         <v>8.1</v>
@@ -27416,19 +28430,19 @@
         <v>7.2</v>
       </c>
       <c r="J3" s="28">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="K3" s="17">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="L3" s="17">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="M3" s="54">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="N3" s="54">
-        <v>52.4</v>
+        <v>52.3</v>
       </c>
       <c r="O3" s="10">
         <v>23</v>
@@ -27437,10 +28451,10 @@
         <v>21</v>
       </c>
       <c r="Q3" s="10">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="R3" s="10" t="s">
-        <v>296</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -27496,7 +28510,7 @@
         <v>17</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -27552,7 +28566,7 @@
         <v>8</v>
       </c>
       <c r="R5" s="10" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -27608,287 +28622,287 @@
         <v>8</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="B7" s="10">
+        <v>7</v>
+      </c>
+      <c r="C7" s="10">
         <v>6</v>
       </c>
-      <c r="C7" s="10">
-        <v>2</v>
-      </c>
       <c r="D7" s="10">
-        <v>4</v>
-      </c>
-      <c r="E7" s="59">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="F7" s="12">
-        <v>2.25</v>
+        <v>1</v>
+      </c>
+      <c r="E7" s="58">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="F7" s="16">
+        <v>7.65</v>
       </c>
       <c r="G7" s="10">
-        <v>10.8</v>
-      </c>
-      <c r="H7" s="13">
-        <v>8.3</v>
+        <v>11</v>
+      </c>
+      <c r="H7" s="10">
+        <v>5.4</v>
       </c>
       <c r="I7" s="10">
-        <v>4.8</v>
+        <v>9.9</v>
       </c>
       <c r="J7" s="14">
-        <v>7.6</v>
+        <v>8.1</v>
       </c>
       <c r="K7" s="17">
-        <v>496</v>
+        <v>580</v>
       </c>
       <c r="L7" s="17">
-        <v>1330</v>
+        <v>1244</v>
       </c>
       <c r="M7" s="54">
-        <v>35</v>
+        <v>29.7</v>
       </c>
       <c r="N7" s="54">
-        <v>52.9</v>
+        <v>57.2</v>
       </c>
       <c r="O7" s="10">
-        <v>17.7</v>
+        <v>17</v>
       </c>
       <c r="P7" s="10">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q7" s="10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="R7" s="10" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="B8" s="24">
+        <v>7</v>
+      </c>
+      <c r="C8" s="24">
+        <v>2</v>
+      </c>
+      <c r="D8" s="24">
         <v>5</v>
       </c>
-      <c r="C8" s="24">
-        <v>4</v>
-      </c>
-      <c r="D8" s="24">
-        <v>1</v>
-      </c>
-      <c r="E8" s="58">
-        <v>0.8</v>
-      </c>
-      <c r="F8" s="16">
-        <v>8.28</v>
+      <c r="E8" s="59">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="F8" s="26">
+        <v>1.93</v>
       </c>
       <c r="G8" s="24">
-        <v>11.4</v>
+        <v>9.3</v>
       </c>
       <c r="H8" s="13">
-        <v>6.2</v>
+        <v>7.1</v>
       </c>
       <c r="I8" s="24">
-        <v>9.8</v>
-      </c>
-      <c r="J8" s="27">
-        <v>7.7</v>
+        <v>4.1</v>
+      </c>
+      <c r="J8" s="28">
+        <v>6.5</v>
       </c>
       <c r="K8" s="29">
-        <v>580</v>
+        <v>487</v>
       </c>
       <c r="L8" s="29">
-        <v>1110</v>
+        <v>1176</v>
       </c>
       <c r="M8" s="57">
-        <v>27.9</v>
+        <v>44.3</v>
       </c>
       <c r="N8" s="57">
-        <v>57.7</v>
+        <v>45.3</v>
       </c>
       <c r="O8" s="24">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="P8" s="24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="24">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R8" s="24" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B9" s="10">
         <v>4</v>
       </c>
       <c r="C9" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="10">
-        <v>2</v>
-      </c>
-      <c r="E9" s="53">
-        <v>0.5</v>
-      </c>
-      <c r="F9" s="16">
-        <v>4.37</v>
+        <v>3</v>
+      </c>
+      <c r="E9" s="59">
+        <v>0.25</v>
+      </c>
+      <c r="F9" s="12">
+        <v>2.27</v>
       </c>
       <c r="G9" s="10">
-        <v>11.5</v>
+        <v>7.8</v>
       </c>
       <c r="H9" s="13">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="I9" s="10">
+        <v>9.5</v>
+      </c>
+      <c r="J9" s="28">
+        <v>5.9</v>
+      </c>
+      <c r="K9" s="17">
+        <v>450</v>
+      </c>
+      <c r="L9" s="17">
+        <v>937</v>
+      </c>
+      <c r="M9" s="54">
+        <v>26.3</v>
+      </c>
+      <c r="N9" s="54">
+        <v>57.2</v>
+      </c>
+      <c r="O9" s="10">
+        <v>39.5</v>
+      </c>
+      <c r="P9" s="10">
         <v>3</v>
       </c>
-      <c r="J9" s="14">
-        <v>8.8</v>
-      </c>
-      <c r="K9" s="17">
-        <v>558</v>
-      </c>
-      <c r="L9" s="17">
-        <v>1031</v>
-      </c>
-      <c r="M9" s="54">
-        <v>30.4</v>
-      </c>
-      <c r="N9" s="54">
-        <v>51.4</v>
-      </c>
-      <c r="O9" s="10">
-        <v>17.3</v>
-      </c>
-      <c r="P9" s="10">
-        <v>1</v>
-      </c>
       <c r="Q9" s="10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R9" s="10" t="s">
-        <v>329</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="55" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="B10" s="24">
+        <v>4</v>
+      </c>
+      <c r="C10" s="24">
+        <v>2</v>
+      </c>
+      <c r="D10" s="24">
+        <v>2</v>
+      </c>
+      <c r="E10" s="56">
+        <v>0.5</v>
+      </c>
+      <c r="F10" s="16">
+        <v>4.37</v>
+      </c>
+      <c r="G10" s="24">
+        <v>11.5</v>
+      </c>
+      <c r="H10" s="13">
+        <v>7.8</v>
+      </c>
+      <c r="I10" s="24">
         <v>3</v>
       </c>
-      <c r="C10" s="24">
+      <c r="J10" s="27">
+        <v>8.8</v>
+      </c>
+      <c r="K10" s="29">
+        <v>558</v>
+      </c>
+      <c r="L10" s="29">
+        <v>1031</v>
+      </c>
+      <c r="M10" s="57">
+        <v>30.4</v>
+      </c>
+      <c r="N10" s="57">
+        <v>51.4</v>
+      </c>
+      <c r="O10" s="24">
+        <v>17.3</v>
+      </c>
+      <c r="P10" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="24">
         <v>3</v>
       </c>
-      <c r="D10" s="24">
-        <v>0</v>
-      </c>
-      <c r="E10" s="58">
-        <v>1</v>
-      </c>
-      <c r="F10" s="45">
-        <v>3.92</v>
-      </c>
-      <c r="G10" s="24">
-        <v>6</v>
-      </c>
-      <c r="H10" s="24">
-        <v>5</v>
-      </c>
-      <c r="I10" s="24">
-        <v>9.3</v>
-      </c>
-      <c r="J10" s="28">
-        <v>1.1</v>
-      </c>
-      <c r="K10" s="29">
-        <v>358</v>
-      </c>
-      <c r="L10" s="29">
-        <v>767</v>
-      </c>
-      <c r="M10" s="57">
-        <v>18.6</v>
-      </c>
-      <c r="N10" s="57">
-        <v>42.1</v>
-      </c>
-      <c r="O10" s="24">
-        <v>49.3</v>
-      </c>
-      <c r="P10" s="24">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="24">
-        <v>0</v>
-      </c>
       <c r="R10" s="24" t="s">
-        <v>437</v>
+        <v>329</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="52" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="B11" s="10">
         <v>3</v>
       </c>
       <c r="C11" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D11" s="10">
-        <v>2</v>
-      </c>
-      <c r="E11" s="59">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="F11" s="12">
-        <v>2.02</v>
+        <v>0</v>
+      </c>
+      <c r="E11" s="58">
+        <v>1</v>
+      </c>
+      <c r="F11" s="45">
+        <v>3.92</v>
       </c>
       <c r="G11" s="10">
         <v>6</v>
       </c>
-      <c r="H11" s="13">
-        <v>7.7</v>
+      <c r="H11" s="10">
+        <v>5</v>
       </c>
       <c r="I11" s="10">
-        <v>11</v>
+        <v>9.3</v>
       </c>
       <c r="J11" s="28">
-        <v>5.2</v>
+        <v>1.1</v>
       </c>
       <c r="K11" s="17">
-        <v>419</v>
+        <v>358</v>
       </c>
       <c r="L11" s="17">
-        <v>807</v>
+        <v>767</v>
       </c>
       <c r="M11" s="54">
-        <v>22.7</v>
+        <v>18.6</v>
       </c>
       <c r="N11" s="54">
-        <v>51.2</v>
+        <v>42.1</v>
       </c>
       <c r="O11" s="10">
-        <v>48.3</v>
+        <v>49.3</v>
       </c>
       <c r="P11" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q11" s="10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R11" s="10" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
     </row>
     <row r="12" ht="20" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -28920,7 +29934,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="60" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="B1" s="60"/>
       <c r="C1" s="60"/>
@@ -28930,59 +29944,59 @@
     </row>
     <row r="2" ht="26" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="61" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="B2" s="61" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="C2" s="61" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="D2" s="61" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="E2" s="61" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="F2" s="61" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="B3" s="10">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C3" s="10">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D3" s="10">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E3" s="10">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3" s="10">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="55" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="B4" s="24">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C4" s="24">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4" s="24">
         <v>35</v>
       </c>
       <c r="E4" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="24">
         <v>42</v>
@@ -28990,90 +30004,90 @@
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="52" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="B5" s="10">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C5" s="10">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D5" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="10">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F5" s="10">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="B6" s="56">
-        <v>45.5</v>
+        <v>46.6</v>
       </c>
       <c r="C6" s="56">
-        <v>52.6</v>
+        <v>52</v>
       </c>
       <c r="D6" s="56">
-        <v>53</v>
+        <v>52.2</v>
       </c>
       <c r="E6" s="56">
-        <v>51.7</v>
+        <v>51.6</v>
       </c>
       <c r="F6" s="58">
-        <v>56.8</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="52" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="B7" s="45">
-        <v>3.77</v>
+        <v>3.83</v>
       </c>
       <c r="C7" s="45">
-        <v>3.19</v>
+        <v>3.12</v>
       </c>
       <c r="D7" s="45">
-        <v>3.55</v>
+        <v>3.51</v>
       </c>
       <c r="E7" s="12">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="F7" s="16">
-        <v>4.12</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="55" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="B8" s="24">
         <v>10.6</v>
       </c>
       <c r="C8" s="24">
-        <v>10.9</v>
+        <v>10.7</v>
       </c>
       <c r="D8" s="24">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="E8" s="24">
-        <v>9</v>
+        <v>8.8</v>
       </c>
       <c r="F8" s="24">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="52" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="B9" s="10">
-        <v>8.7</v>
+        <v>8.5</v>
       </c>
       <c r="C9" s="10">
         <v>7.5</v>
@@ -29082,7 +30096,7 @@
         <v>7.4</v>
       </c>
       <c r="E9" s="10">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="F9" s="10">
         <v>7</v>
@@ -29090,19 +30104,19 @@
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="55" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="B10" s="24">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="C10" s="24">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="D10" s="24">
         <v>5.9</v>
       </c>
       <c r="E10" s="24">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="F10" s="24">
         <v>5.7</v>
@@ -29110,19 +30124,19 @@
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="52" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B11" s="10">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="C11" s="10">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="D11" s="10">
         <v>7.3</v>
       </c>
       <c r="E11" s="10">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="F11" s="10">
         <v>7.3</v>
@@ -29130,139 +30144,139 @@
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="55" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="B12" s="24">
-        <v>1018</v>
+        <v>1043</v>
       </c>
       <c r="C12" s="24">
-        <v>1108</v>
+        <v>1092</v>
       </c>
       <c r="D12" s="24">
-        <v>1161</v>
+        <v>1153</v>
       </c>
       <c r="E12" s="24">
-        <v>987</v>
+        <v>961</v>
       </c>
       <c r="F12" s="24">
-        <v>1181</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="52" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="B13" s="10">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="C13" s="10">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D13" s="10">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E13" s="10">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F13" s="10">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="55" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="B14" s="24">
-        <v>25.2</v>
+        <v>25.7</v>
       </c>
       <c r="C14" s="24">
-        <v>29.1</v>
+        <v>29.8</v>
       </c>
       <c r="D14" s="24">
-        <v>30.9</v>
+        <v>30.8</v>
       </c>
       <c r="E14" s="24">
-        <v>25.2</v>
+        <v>27.5</v>
       </c>
       <c r="F14" s="24">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="52" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="B15" s="10">
-        <v>51</v>
+        <v>51.6</v>
       </c>
       <c r="C15" s="10">
-        <v>56.1</v>
+        <v>55.4</v>
       </c>
       <c r="D15" s="10">
-        <v>57.4</v>
+        <v>57.3</v>
       </c>
       <c r="E15" s="10">
-        <v>53.2</v>
+        <v>51.3</v>
       </c>
       <c r="F15" s="10">
-        <v>57.2</v>
+        <v>57.1</v>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="55" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="B16" s="24">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="C16" s="24">
-        <v>20</v>
+        <v>19.8</v>
       </c>
       <c r="D16" s="24">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="E16" s="24">
-        <v>20.4</v>
+        <v>20.1</v>
       </c>
       <c r="F16" s="24">
-        <v>20</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="52" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="B17" s="10">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="C17" s="10">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="D17" s="10">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="E17" s="10">
-        <v>680</v>
+        <v>667</v>
       </c>
       <c r="F17" s="10">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="55" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B18" s="24">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="C18" s="24">
         <v>12.3</v>
       </c>
       <c r="D18" s="24">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="E18" s="24">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="F18" s="24">
         <v>11</v>
@@ -29270,7 +30284,7 @@
     </row>
     <row r="19" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="52" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="B19" s="10">
         <v>19</v>
@@ -29282,7 +30296,7 @@
         <v>23</v>
       </c>
       <c r="E19" s="10">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="10">
         <v>23</v>
@@ -29290,7 +30304,7 @@
     </row>
     <row r="20" ht="22" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="55" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="B20" s="24">
         <v>5</v>
@@ -29330,7 +30344,7 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="62" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="B1" s="62"/>
       <c r="C1" s="62"/>
@@ -29342,15 +30356,15 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="63" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="B2" s="10">
-        <v>150</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="64" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="B3" s="56">
         <v>0.5</v>
@@ -29358,39 +30372,39 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="63" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="64" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="63" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="64" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B7" s="24">
-        <v>1075</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="63" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="B8" s="10">
         <v>499</v>
@@ -29398,31 +30412,31 @@
     </row>
     <row r="9" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="64" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="63" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="64" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B11" s="24" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="62" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="B13" s="62"/>
       <c r="C13" s="62"/>
@@ -29434,15 +30448,15 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="63" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="64" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="B15" s="56">
         <v>0.4</v>
@@ -29450,7 +30464,7 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="63" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="B16" s="53">
         <v>0.5</v>
@@ -29458,31 +30472,31 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="64" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="63" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="64" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="B19" s="24" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="63" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="B20" s="10">
         <v>1241</v>
@@ -29490,7 +30504,7 @@
     </row>
     <row r="22" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="62" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B22" s="62"/>
       <c r="C22" s="62"/>
@@ -29502,137 +30516,137 @@
     </row>
     <row r="23" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="65" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="B23" s="65" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="C23" s="65" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="D23" s="65" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="E23" s="65" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="F23" s="65" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="G23" s="65" t="s">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="H23" s="65" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="52" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="B24" s="10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C24" s="58">
-        <v>0.5833333333333334</v>
+        <v>0.56</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="F24" s="10" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="G24" s="10" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="55" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="B25" s="24">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C25" s="58">
-        <v>0.7727272727272727</v>
+        <v>0.6956521739130435</v>
       </c>
       <c r="D25" s="33" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="E25" s="24" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="F25" s="33" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="G25" s="24" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="H25" s="24" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="52" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="B26" s="10">
-        <v>22</v>
-      </c>
-      <c r="C26" s="53">
-        <v>0.5454545454545454</v>
+        <v>23</v>
+      </c>
+      <c r="C26" s="58">
+        <v>0.5652173913043478</v>
       </c>
       <c r="D26" s="33" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="F26" s="10" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="G26" s="10" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="55" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="B27" s="24">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C27" s="59">
-        <v>0.3902439024390244</v>
+        <v>0.4117647058823529</v>
       </c>
       <c r="D27" s="66" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E27" s="24" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="F27" s="24" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="G27" s="24" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
       <c r="H27" s="24" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="67" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="B28" s="67"/>
       <c r="C28" s="67"/>
@@ -29644,7 +30658,7 @@
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="62" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="B30" s="62"/>
       <c r="C30" s="62"/>
@@ -29656,19 +30670,19 @@
     </row>
     <row r="31" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="65" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
       <c r="B31" s="65" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C31" s="65" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="D31" s="65" t="s">
         <v>9</v>
       </c>
       <c r="E31" s="65" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="F31" s="65" t="s">
         <v>20</v>
@@ -29677,12 +30691,12 @@
         <v>27</v>
       </c>
       <c r="H31" s="65" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="52" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="B32" s="10">
         <v>5</v>
@@ -29691,10 +30705,10 @@
         <v>0.6</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="F32" s="10">
         <v>972</v>
@@ -29703,12 +30717,12 @@
         <v>5</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="55" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="B33" s="24">
         <v>0</v>
@@ -29729,12 +30743,12 @@
         <v>75</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="52" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="B34" s="10">
         <v>19</v>
@@ -29743,10 +30757,10 @@
         <v>0.7368421052631579</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="F34" s="10">
         <v>1240</v>
@@ -29755,24 +30769,24 @@
         <v>6</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="55" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
       <c r="B35" s="24">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="C35" s="56">
-        <v>0.4603174603174603</v>
+        <v>0.4621212121212121</v>
       </c>
       <c r="D35" s="24" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="E35" s="24" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="F35" s="24">
         <v>1054</v>
@@ -29781,12 +30795,12 @@
         <v>6</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="62" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="B37" s="62"/>
       <c r="C37" s="62"/>
@@ -29798,19 +30812,19 @@
     </row>
     <row r="38" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="65" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B38" s="65" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C38" s="65" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="D38" s="65" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="65" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="F38" s="65" t="s">
         <v>20</v>
@@ -29819,64 +30833,64 @@
         <v>27</v>
       </c>
       <c r="H38" s="65" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="52" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="B39" s="10">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C39" s="58">
-        <v>0.56</v>
+        <v>0.5512820512820513</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="F39" s="10">
-        <v>1135</v>
+        <v>1119</v>
       </c>
       <c r="G39" s="10">
         <v>6</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="55" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B40" s="24">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C40" s="59">
-        <v>0.43243243243243246</v>
+        <v>0.44155844155844154</v>
       </c>
       <c r="D40" s="24" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="E40" s="24" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="F40" s="24">
-        <v>1021</v>
+        <v>1013</v>
       </c>
       <c r="G40" s="24">
         <v>6</v>
       </c>
       <c r="H40" s="24" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
     </row>
     <row r="42" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="62" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="B42" s="62"/>
       <c r="C42" s="62"/>
@@ -29888,7 +30902,7 @@
     </row>
     <row r="43" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="65" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="B43" s="65" t="s">
         <v>26</v>
@@ -29914,7 +30928,7 @@
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="52" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="B44" s="10">
         <v>24</v>
@@ -29940,10 +30954,10 @@
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="55" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="B45" s="24">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C45" s="24">
         <v>6</v>
@@ -29966,7 +30980,7 @@
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="52" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="B46" s="10">
         <v>24</v>
@@ -29992,7 +31006,7 @@
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="55" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="B47" s="24">
         <v>21</v>
@@ -30013,12 +31027,12 @@
         <v>0</v>
       </c>
       <c r="H47" s="24">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="49" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="62" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="B49" s="62"/>
       <c r="C49" s="62"/>
@@ -30030,137 +31044,137 @@
     </row>
     <row r="50" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="65" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
       <c r="B50" s="65" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="C50" s="65" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="D50" s="65" t="s">
         <v>9</v>
       </c>
       <c r="E50" s="65" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="F50" s="65" t="s">
         <v>20</v>
       </c>
       <c r="G50" s="65" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H50" s="65" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="52" t="s">
+        <v>561</v>
+      </c>
+      <c r="B51" s="10">
+        <v>48</v>
+      </c>
+      <c r="C51" s="58">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="D51" s="10" t="s">
+        <v>562</v>
+      </c>
+      <c r="E51" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="F51" s="10">
+        <v>1010</v>
+      </c>
+      <c r="G51" s="10" t="s">
         <v>550</v>
       </c>
-      <c r="B51" s="10">
-        <v>46</v>
-      </c>
-      <c r="C51" s="58">
-        <v>0.5869565217391305</v>
-      </c>
-      <c r="D51" s="10" t="s">
-        <v>551</v>
-      </c>
-      <c r="E51" s="10" t="s">
-        <v>552</v>
-      </c>
-      <c r="F51" s="10">
-        <v>1030</v>
-      </c>
-      <c r="G51" s="10" t="s">
-        <v>539</v>
-      </c>
       <c r="H51" s="10" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="55" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="B52" s="24">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C52" s="56">
-        <v>0.46296296296296297</v>
+        <v>0.4642857142857143</v>
       </c>
       <c r="D52" s="24" t="s">
-        <v>555</v>
+        <v>542</v>
       </c>
       <c r="E52" s="24" t="s">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="F52" s="24">
         <v>1113</v>
       </c>
       <c r="G52" s="24" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H52" s="24" t="s">
-        <v>557</v>
+        <v>567</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="52" t="s">
-        <v>558</v>
+        <v>568</v>
       </c>
       <c r="B53" s="10">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C53" s="58">
-        <v>0.5806451612903226</v>
+        <v>0.59375</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>559</v>
+        <v>569</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>560</v>
+        <v>570</v>
       </c>
       <c r="F53" s="10">
-        <v>1205</v>
+        <v>1240</v>
       </c>
       <c r="G53" s="10" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="55" t="s">
-        <v>561</v>
+        <v>571</v>
       </c>
       <c r="B54" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C54" s="59">
-        <v>0.2631578947368421</v>
+        <v>0.25</v>
       </c>
       <c r="D54" s="24" t="s">
-        <v>562</v>
+        <v>572</v>
       </c>
       <c r="E54" s="24" t="s">
-        <v>563</v>
+        <v>573</v>
       </c>
       <c r="F54" s="24">
-        <v>862</v>
+        <v>852</v>
       </c>
       <c r="G54" s="24" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H54" s="24" t="s">
-        <v>564</v>
+        <v>574</v>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="62" t="s">
-        <v>565</v>
+        <v>575</v>
       </c>
       <c r="B56" s="62"/>
       <c r="C56" s="62"/>
@@ -30172,10 +31186,10 @@
     </row>
     <row r="57" ht="26" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="65" t="s">
-        <v>566</v>
+        <v>576</v>
       </c>
       <c r="B57" s="65" t="s">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="C57" s="65" t="s">
         <v>5</v>
@@ -30190,15 +31204,15 @@
         <v>6</v>
       </c>
       <c r="G57" s="65" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H57" s="65" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="63" t="s">
-        <v>568</v>
+        <v>578</v>
       </c>
       <c r="B58" s="68">
         <v>31</v>
@@ -30216,15 +31230,15 @@
         <v>58</v>
       </c>
       <c r="G58" s="10" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H58" s="10" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="64" t="s">
-        <v>569</v>
+        <v>579</v>
       </c>
       <c r="B59" s="69">
         <v>2536</v>
@@ -30242,15 +31256,15 @@
         <v>58</v>
       </c>
       <c r="G59" s="24" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="63" t="s">
-        <v>570</v>
+        <v>580</v>
       </c>
       <c r="B60" s="70">
         <v>11.2</v>
@@ -30268,15 +31282,15 @@
         <v>58</v>
       </c>
       <c r="G60" s="10" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="64" t="s">
-        <v>571</v>
+        <v>581</v>
       </c>
       <c r="B61" s="69">
         <v>756</v>
@@ -30294,15 +31308,15 @@
         <v>58</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="63" t="s">
-        <v>572</v>
+        <v>582</v>
       </c>
       <c r="B62" s="71">
         <v>116</v>
@@ -30320,10 +31334,10 @@
         <v>162</v>
       </c>
       <c r="G62" s="10" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
   </sheetData>
